--- a/output/yearly_surface_area_iteration_50_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_50_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497629432811</v>
+        <v>10.84497648726365</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907180989331</v>
+        <v>37.78907248217278</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.34994415106837</v>
+        <v>5.907175936453058</v>
       </c>
       <c r="C2" t="n">
-        <v>5.276893910326605</v>
+        <v>7.384706231344508</v>
       </c>
       <c r="D2" t="n">
-        <v>31.80371687907542</v>
+        <v>30.55689729468197</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.40286071610646</v>
+        <v>20.51852701875834</v>
       </c>
       <c r="C3" t="n">
-        <v>16.56208377064369</v>
+        <v>30.15438073594078</v>
       </c>
       <c r="D3" t="n">
-        <v>77.51879872732815</v>
+        <v>72.27626598665017</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.168788156335</v>
+        <v>39.52614432068083</v>
       </c>
       <c r="C4" t="n">
-        <v>47.06891193240908</v>
+        <v>76.16791388628454</v>
       </c>
       <c r="D4" t="n">
-        <v>97.23916486253384</v>
+        <v>81.030510265419</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.65755964432967</v>
+        <v>47.98291904506286</v>
       </c>
       <c r="C5" t="n">
-        <v>97.53663441692063</v>
+        <v>131.0387748243431</v>
       </c>
       <c r="D5" t="n">
-        <v>62.85639676440205</v>
+        <v>56.49958037940395</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.861722109084</v>
+        <v>43.51203999992289</v>
       </c>
       <c r="C6" t="n">
-        <v>132.0254312671111</v>
+        <v>136.734875004383</v>
       </c>
       <c r="D6" t="n">
-        <v>42.66675522656639</v>
+        <v>41.45920555034281</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.62579956042849</v>
+        <v>29.64387192973244</v>
       </c>
       <c r="C7" t="n">
-        <v>112.347280283188</v>
+        <v>107.9755577561769</v>
       </c>
       <c r="D7" t="n">
-        <v>38.20765715387736</v>
+        <v>38.14777054391831</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.85384276525424</v>
+        <v>14.77039421039326</v>
       </c>
       <c r="C8" t="n">
-        <v>64.58918146239766</v>
+        <v>64.75607857211961</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>36.0546844384641</v>
+        <v>36.49843440078366</v>
       </c>
       <c r="D9" t="n">
         <v>34.39062207976576</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.696661019691585</v>
+        <v>7.695380667605328</v>
       </c>
       <c r="C21" t="n">
-        <v>94.2840974912219</v>
+        <v>94.26841317816526</v>
       </c>
       <c r="D21" t="n">
-        <v>8.658743647153033</v>
+        <v>8.657303251055994</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.17541404389069</v>
+        <v>6.219371706403543</v>
       </c>
       <c r="C2" t="n">
-        <v>8.871072255574179</v>
+        <v>6.089781009442965</v>
       </c>
       <c r="D2" t="n">
-        <v>29.95312245657018</v>
+        <v>30.12591005251763</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.75767254796706</v>
+        <v>19.99820073550753</v>
       </c>
       <c r="C3" t="n">
-        <v>18.50103548653114</v>
+        <v>29.23644663247001</v>
       </c>
       <c r="D3" t="n">
-        <v>83.38964999872408</v>
+        <v>78.36801049150165</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.80768492762142</v>
+        <v>38.83695743229957</v>
       </c>
       <c r="C4" t="n">
-        <v>43.71231653158923</v>
+        <v>74.89164187076368</v>
       </c>
       <c r="D4" t="n">
-        <v>110.3720039022434</v>
+        <v>96.00118100747861</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.59713325502288</v>
+        <v>52.94074495150926</v>
       </c>
       <c r="C5" t="n">
-        <v>92.18610942877551</v>
+        <v>135.4075521082413</v>
       </c>
       <c r="D5" t="n">
-        <v>81.19053514121123</v>
+        <v>69.48319376806802</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.52211951887262</v>
+        <v>53.65545728020094</v>
       </c>
       <c r="C6" t="n">
-        <v>142.0078419238926</v>
+        <v>168.5739348008113</v>
       </c>
       <c r="D6" t="n">
-        <v>50.91834468076083</v>
+        <v>48.74475526355839</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.50709020367265</v>
+        <v>39.64493579289469</v>
       </c>
       <c r="C7" t="n">
-        <v>150.195617777311</v>
+        <v>148.9379989681709</v>
       </c>
       <c r="D7" t="n">
-        <v>41.74096714146164</v>
+        <v>40.8426679920758</v>
       </c>
     </row>
     <row r="8">
@@ -1178,10 +1178,10 @@
         <v>22.5311098124643</v>
       </c>
       <c r="C8" t="n">
-        <v>103.5596565824748</v>
+        <v>101.6403398206723</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -1192,10 +1192,10 @@
         <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>57.02187015806322</v>
+        <v>56.46718270516377</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>36.15776794741003</v>
+        <v>36.30012136452581</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>31.8076438698924</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.879228944074787</v>
+        <v>7.873737902204783</v>
       </c>
       <c r="C21" t="n">
-        <v>103.4148798909816</v>
+        <v>102.3585927286622</v>
       </c>
       <c r="D21" t="n">
-        <v>9.849036180093483</v>
+        <v>9.842172377755979</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.194648087348126</v>
+        <v>7.822565707438585</v>
       </c>
       <c r="C2" t="n">
-        <v>9.971611432034853</v>
+        <v>8.430267536367362</v>
       </c>
       <c r="D2" t="n">
-        <v>37.8748446821377</v>
+        <v>30.98003055521235</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.74985962406209</v>
+        <v>20.18473279931442</v>
       </c>
       <c r="C3" t="n">
-        <v>25.91323065359456</v>
+        <v>26.3942870286755</v>
       </c>
       <c r="D3" t="n">
-        <v>86.41343292780425</v>
+        <v>82.02011195129978</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.38651516249953</v>
+        <v>37.56068541677872</v>
       </c>
       <c r="C4" t="n">
-        <v>44.31216437888403</v>
+        <v>73.09209832887927</v>
       </c>
       <c r="D4" t="n">
-        <v>123.3644530202457</v>
+        <v>107.6663072293392</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.4070751110265</v>
+        <v>54.68334712654735</v>
       </c>
       <c r="C5" t="n">
-        <v>86.73740967020571</v>
+        <v>136.217493964245</v>
       </c>
       <c r="D5" t="n">
-        <v>96.80032363873553</v>
+        <v>83.9394287131023</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.61270234957058</v>
+        <v>60.78000036992004</v>
       </c>
       <c r="C6" t="n">
-        <v>143.0946366324939</v>
+        <v>186.9689415352838</v>
       </c>
       <c r="D6" t="n">
-        <v>62.06805335789186</v>
+        <v>56.39256987964104</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.26860762699867</v>
+        <v>49.58611304609789</v>
       </c>
       <c r="C7" t="n">
-        <v>173.7909421011789</v>
+        <v>188.3433883212293</v>
       </c>
       <c r="D7" t="n">
-        <v>45.51382356888213</v>
+        <v>44.73529763941441</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.95941385342316</v>
+        <v>31.12631096314512</v>
       </c>
       <c r="C8" t="n">
-        <v>145.9515224518521</v>
+        <v>143.0308230317178</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>39.72151211382594</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.75312366234431</v>
+        <v>15.53124868118453</v>
       </c>
       <c r="C9" t="n">
-        <v>87.19686759579318</v>
+        <v>85.08905527477528</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>37.05312185368311</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>49.53898915629405</v>
+        <v>49.25428232206248</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.07235589714055</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
         <v>35.79943003535993</v>
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.046875938955704</v>
+        <v>8.035898133354854</v>
       </c>
       <c r="C21" t="n">
-        <v>111.6504036530104</v>
+        <v>110.4935993336292</v>
       </c>
       <c r="D21" t="n">
-        <v>11.06445441606409</v>
+        <v>11.04935993336292</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.619343932659496</v>
+        <v>7.161849502480481</v>
       </c>
       <c r="C2" t="n">
-        <v>6.700428081484481</v>
+        <v>5.799183688985909</v>
       </c>
       <c r="D2" t="n">
-        <v>30.96334084424015</v>
+        <v>25.57060070481242</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.7343726449724</v>
+        <v>25.02965771977243</v>
       </c>
       <c r="C3" t="n">
-        <v>38.12617209442488</v>
+        <v>41.6604638297134</v>
       </c>
       <c r="D3" t="n">
-        <v>93.7569057555704</v>
+        <v>87.52280783360315</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.65306751196916</v>
+        <v>26.26567807941916</v>
       </c>
       <c r="C4" t="n">
-        <v>67.96148482648545</v>
+        <v>107.9853752332194</v>
       </c>
       <c r="D4" t="n">
-        <v>116.0131262108456</v>
+        <v>100.4426076214912</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.57577148524092</v>
+        <v>34.23845118560752</v>
       </c>
       <c r="C5" t="n">
-        <v>85.48568134729102</v>
+        <v>111.722888743287</v>
       </c>
       <c r="D5" t="n">
-        <v>64.03449400949822</v>
+        <v>56.25414345334224</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.94723197034471</v>
+        <v>30.79251674370121</v>
       </c>
       <c r="C6" t="n">
-        <v>114.435457650121</v>
+        <v>124.0556034040355</v>
       </c>
       <c r="D6" t="n">
-        <v>29.94723197034471</v>
+        <v>29.46421209985528</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.48122060599696</v>
+        <v>20.60099382591507</v>
       </c>
       <c r="C7" t="n">
-        <v>102.645649469821</v>
+        <v>100.5496181212541</v>
       </c>
       <c r="D7" t="n">
-        <v>28.20659329071511</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>64.25538724295374</v>
+        <v>62.66986470059513</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>37.82968428774233</v>
+        <v>37.60780930658255</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>28.18597658892593</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.47068342315751</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
         <v>28.60910984945629</v>
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>26.4698816019025</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.594579255875073</v>
+        <v>4.496404485450391</v>
       </c>
       <c r="C2" t="n">
-        <v>3.166136346195963</v>
+        <v>2.675262494072558</v>
       </c>
       <c r="D2" t="n">
-        <v>22.2689831754304</v>
+        <v>18.71898347687393</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.85218236948201</v>
+        <v>25.53034904893831</v>
       </c>
       <c r="C3" t="n">
-        <v>32.59893251951534</v>
+        <v>32.62347621212151</v>
       </c>
       <c r="D3" t="n">
-        <v>96.65797022161972</v>
+        <v>88.80398858764524</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.89251614081414</v>
+        <v>35.63351467334223</v>
       </c>
       <c r="C4" t="n">
-        <v>83.81278325925445</v>
+        <v>108.9936301254809</v>
       </c>
       <c r="D4" t="n">
-        <v>134.3276296335698</v>
+        <v>116.651262218606</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.18369429834795</v>
+        <v>38.26361677301944</v>
       </c>
       <c r="C5" t="n">
-        <v>106.4705385255666</v>
+        <v>154.3552828002048</v>
       </c>
       <c r="D5" t="n">
-        <v>83.15403054970486</v>
+        <v>72.69841749947632</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.18623863083319</v>
+        <v>36.58875518957439</v>
       </c>
       <c r="C6" t="n">
-        <v>129.1675637000486</v>
+        <v>152.0707558924225</v>
       </c>
       <c r="D6" t="n">
-        <v>37.63529824230149</v>
+        <v>35.98498035146259</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.22360179685679</v>
+        <v>19.3433750167749</v>
       </c>
       <c r="C7" t="n">
-        <v>130.1934900509865</v>
+        <v>130.6126963206999</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>30.3625112492411</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>86.20235717139117</v>
+        <v>85.11752595819846</v>
       </c>
       <c r="D8" t="n">
-        <v>28.37250865273282</v>
+        <v>28.45595720759379</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>43.93124626963626</v>
+        <v>42.3781214015178</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.966661635784614</v>
+        <v>5.499750639190632</v>
       </c>
       <c r="C2" t="n">
-        <v>6.056401587498573</v>
+        <v>3.372303364087794</v>
       </c>
       <c r="D2" t="n">
-        <v>22.27781890476862</v>
+        <v>19.4965276586374</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.66226309420587</v>
+        <v>20.38599107868502</v>
       </c>
       <c r="C3" t="n">
-        <v>21.60335823195106</v>
+        <v>20.90631736193583</v>
       </c>
       <c r="D3" t="n">
-        <v>93.05004740851268</v>
+        <v>83.48782476914876</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.6011991145601</v>
+        <v>41.69580674706629</v>
       </c>
       <c r="C4" t="n">
-        <v>82.5365112437336</v>
+        <v>94.89082435397546</v>
       </c>
       <c r="D4" t="n">
-        <v>148.0347910802638</v>
+        <v>131.7367974420625</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.19122948481243</v>
+        <v>45.38128762880881</v>
       </c>
       <c r="C5" t="n">
-        <v>131.5296486764665</v>
+        <v>178.604451095101</v>
       </c>
       <c r="D5" t="n">
-        <v>109.1948884048515</v>
+        <v>93.7569057555704</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.66675522656639</v>
+        <v>43.83405324691584</v>
       </c>
       <c r="C6" t="n">
-        <v>148.3676035520035</v>
+        <v>195.2205309894783</v>
       </c>
       <c r="D6" t="n">
-        <v>52.28690098048088</v>
+        <v>47.45670227558657</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.98511922018283</v>
+        <v>28.7455727803466</v>
       </c>
       <c r="C7" t="n">
-        <v>158.6995163914969</v>
+        <v>173.0723027816702</v>
       </c>
       <c r="D7" t="n">
-        <v>34.37491411649782</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -2422,7 +2422,7 @@
         <v>13.51866588747858</v>
       </c>
       <c r="C8" t="n">
-        <v>126.1742149498001</v>
+        <v>124.8390380720244</v>
       </c>
       <c r="D8" t="n">
         <v>29.87458264023044</v>
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>71.33280644286897</v>
+        <v>69.11405663127118</v>
       </c>
       <c r="D9" t="n">
         <v>29.39843500367073</v>
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>40.9977841293468</v>
+        <v>39.71660337530471</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.963896319121121</v>
+        <v>3.246639657944202</v>
       </c>
       <c r="C2" t="n">
-        <v>2.804853191033137</v>
+        <v>1.621847207415731</v>
       </c>
       <c r="D2" t="n">
-        <v>15.3731873008008</v>
+        <v>13.65022007984765</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.63281066307847</v>
+        <v>21.49045724596268</v>
       </c>
       <c r="C3" t="n">
-        <v>23.89573912136737</v>
+        <v>18.90846078379357</v>
       </c>
       <c r="D3" t="n">
-        <v>92.86842408322703</v>
+        <v>83.07058199484386</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.00433756810704</v>
+        <v>45.7543517564226</v>
       </c>
       <c r="C4" t="n">
-        <v>79.88186545145022</v>
+        <v>88.79024411978578</v>
       </c>
       <c r="D4" t="n">
-        <v>160.1976633881775</v>
+        <v>141.8959226856085</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.34478303730243</v>
+        <v>47.36932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>158.1595551541612</v>
+        <v>208.4250376115979</v>
       </c>
       <c r="D5" t="n">
-        <v>118.1287925134975</v>
+        <v>99.50012982541426</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.70321876034376</v>
+        <v>35.66296710446964</v>
       </c>
       <c r="C6" t="n">
-        <v>183.990319000599</v>
+        <v>231.4872729320597</v>
       </c>
       <c r="D6" t="n">
-        <v>50.99884799250906</v>
+        <v>46.85292743747478</v>
       </c>
     </row>
     <row r="7">
@@ -2719,10 +2719,10 @@
         <v>8.92310488389926</v>
       </c>
       <c r="C7" t="n">
-        <v>166.0655694164607</v>
+        <v>174.2101483708923</v>
       </c>
       <c r="D7" t="n">
-        <v>34.61446055633404</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>92.12720456652069</v>
+        <v>88.8727109269425</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>31.28437234352885</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.1930287493049</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.643666641087413</v>
+        <v>3.69038962026376</v>
       </c>
       <c r="C2" t="n">
-        <v>7.216827373918303</v>
+        <v>8.970228773703107</v>
       </c>
       <c r="D2" t="n">
-        <v>18.57270306894116</v>
+        <v>19.41798784229766</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.03684874887165</v>
+        <v>16.49336143134641</v>
       </c>
       <c r="C3" t="n">
-        <v>17.19040230136165</v>
+        <v>12.4976482750619</v>
       </c>
       <c r="D3" t="n">
-        <v>84.44993751931064</v>
+        <v>76.26707040441346</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.43077592464865</v>
+        <v>43.5081130091059</v>
       </c>
       <c r="C4" t="n">
-        <v>70.46297797690632</v>
+        <v>68.29331555052087</v>
       </c>
       <c r="D4" t="n">
-        <v>168.5827705301495</v>
+        <v>148.9537069314388</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.22393025868885</v>
+        <v>56.74501730546565</v>
       </c>
       <c r="C5" t="n">
-        <v>152.8090301660161</v>
+        <v>189.0846078379357</v>
       </c>
       <c r="D5" t="n">
-        <v>144.8323300690107</v>
+        <v>121.4176473227243</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.69192081397831</v>
+        <v>47.01393406097126</v>
       </c>
       <c r="C6" t="n">
-        <v>218.4054847729709</v>
+        <v>278.2194454019121</v>
       </c>
       <c r="D6" t="n">
-        <v>69.51460969460392</v>
+        <v>61.86679507852126</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.12190094624263</v>
+        <v>19.70269467652924</v>
       </c>
       <c r="C7" t="n">
-        <v>210.8607536658342</v>
+        <v>245.8944204918816</v>
       </c>
       <c r="D7" t="n">
-        <v>39.82459562277186</v>
+        <v>38.14777054391831</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>146.6191108907399</v>
+        <v>146.368765226157</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>33.12907627980861</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>61.34843229067891</v>
+        <v>59.57343244140068</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.48478774391545</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.19166178650638</v>
+        <v>2.670353755551324</v>
       </c>
       <c r="C2" t="n">
-        <v>3.89361139504285</v>
+        <v>4.955862411037899</v>
       </c>
       <c r="D2" t="n">
-        <v>13.52848336452105</v>
+        <v>14.12047723018187</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.11047982669016</v>
+        <v>15.00110492089126</v>
       </c>
       <c r="C3" t="n">
-        <v>22.39366513386975</v>
+        <v>23.10052348092745</v>
       </c>
       <c r="D3" t="n">
-        <v>80.86164966028855</v>
+        <v>74.61282552275759</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.46607778427253</v>
+        <v>39.87073776487146</v>
       </c>
       <c r="C4" t="n">
-        <v>60.38042905429158</v>
+        <v>54.39471330149878</v>
       </c>
       <c r="D4" t="n">
-        <v>171.9266032108142</v>
+        <v>153.9056423516597</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.08987279156354</v>
+        <v>61.28560043760715</v>
       </c>
       <c r="C5" t="n">
-        <v>147.7039421039326</v>
+        <v>170.0632460681537</v>
       </c>
       <c r="D5" t="n">
-        <v>163.8536918387927</v>
+        <v>136.3156687346697</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.2252718592916</v>
+        <v>55.58753676215866</v>
       </c>
       <c r="C6" t="n">
-        <v>239.8998690097506</v>
+        <v>299.7138296386918</v>
       </c>
       <c r="D6" t="n">
-        <v>84.52847733565039</v>
+        <v>74.78757661411353</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.92416874706152</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="C7" t="n">
-        <v>251.1045555583194</v>
+        <v>303.8047723222882</v>
       </c>
       <c r="D7" t="n">
-        <v>45.15450390912779</v>
+        <v>42.22006002113408</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>187.2585571080366</v>
+        <v>193.600647277471</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>72.22030636750809</v>
+        <v>68.11561921605218</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>24.16670148773948</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.372704274715294</v>
+        <v>4.765403356414017</v>
       </c>
       <c r="C2" t="n">
-        <v>9.458157382713772</v>
+        <v>8.553967747102458</v>
       </c>
       <c r="D2" t="n">
-        <v>16.3902779224005</v>
+        <v>13.70814319439821</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.50393967191488</v>
+        <v>12.12949288596934</v>
       </c>
       <c r="C3" t="n">
-        <v>18.82992096745382</v>
+        <v>21.13702807243383</v>
       </c>
       <c r="D3" t="n">
-        <v>74.09740797802802</v>
+        <v>69.35556656651592</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.15678619970578</v>
+        <v>34.71459882216722</v>
       </c>
       <c r="C4" t="n">
-        <v>58.18524118759571</v>
+        <v>55.64545987670921</v>
       </c>
       <c r="D4" t="n">
-        <v>172.2073830542288</v>
+        <v>154.9904735648525</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.98540662428588</v>
+        <v>60.62292073724056</v>
       </c>
       <c r="C5" t="n">
-        <v>131.5787360616788</v>
+        <v>140.119941088626</v>
       </c>
       <c r="D5" t="n">
-        <v>179.7089172623787</v>
+        <v>153.6189720220197</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.78378849201678</v>
+        <v>65.73095404243671</v>
       </c>
       <c r="C6" t="n">
-        <v>238.7325709894012</v>
+        <v>289.1678957996726</v>
       </c>
       <c r="D6" t="n">
-        <v>108.1561993337584</v>
+        <v>92.37755023110364</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.91389360612931</v>
+        <v>33.65627479698915</v>
       </c>
       <c r="C7" t="n">
-        <v>293.863595069085</v>
+        <v>356.564875696216</v>
       </c>
       <c r="D7" t="n">
-        <v>54.91602133245383</v>
+        <v>49.88554609589318</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>244.5042657426681</v>
+        <v>276.465062254423</v>
       </c>
       <c r="D8" t="n">
-        <v>37.55184968744049</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>131.6828013183289</v>
+        <v>129.9078014690506</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>50.82016991033614</v>
+        <v>47.97310156802039</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.6997904911455</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
+        <v>19.96089432274615</v>
+      </c>
+      <c r="D12" t="n">
         <v>20.39482680802324</v>
-      </c>
-      <c r="D12" t="n">
-        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.841979677345269</v>
+        <v>4.732023934469626</v>
       </c>
       <c r="C2" t="n">
-        <v>4.437499623195583</v>
+        <v>4.200898426472102</v>
       </c>
       <c r="D2" t="n">
-        <v>4.85081540668349</v>
+        <v>3.717878555982671</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.129811681138832</v>
+        <v>3.406664533736432</v>
       </c>
       <c r="C2" t="n">
-        <v>5.372123437638546</v>
+        <v>4.927391727614741</v>
       </c>
       <c r="D2" t="n">
-        <v>12.06273404208056</v>
+        <v>10.08843940884022</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.80890335503714</v>
+        <v>16.75352457297182</v>
       </c>
       <c r="C3" t="n">
-        <v>27.05696672904209</v>
+        <v>27.84236489243954</v>
       </c>
       <c r="D3" t="n">
-        <v>80.8272884906399</v>
+        <v>74.97116343480768</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.22581163863931</v>
+        <v>46.58392856651115</v>
       </c>
       <c r="C4" t="n">
-        <v>82.03876515768046</v>
+        <v>81.77074803442109</v>
       </c>
       <c r="D4" t="n">
-        <v>175.2704358914788</v>
+        <v>157.5430175958942</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.95713156284519</v>
+        <v>38.7054032399305</v>
       </c>
       <c r="C5" t="n">
-        <v>198.5830168765236</v>
+        <v>228.3545160078081</v>
       </c>
       <c r="D5" t="n">
-        <v>163.4119053718816</v>
+        <v>138.2055330653448</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.65539086027615</v>
+        <v>20.89060939866788</v>
       </c>
       <c r="C6" t="n">
-        <v>242.6772332650649</v>
+        <v>291.5024918403715</v>
       </c>
       <c r="D6" t="n">
-        <v>84.44797402390215</v>
+        <v>73.82153687313468</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.407867265618931</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>171.9344571924481</v>
+        <v>194.3919359270939</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>31.91956310817654</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>97.05066930331843</v>
+        <v>95.71549242554278</v>
       </c>
       <c r="D8" t="n">
-        <v>25.2849121228766</v>
+        <v>24.36697801940583</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>38.71718421238145</v>
+        <v>36.60937189136354</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>19.96874830438012</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.34948648717864</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>19.3600647277471</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
+        <v>15.99267010218054</v>
+      </c>
+      <c r="D11" t="n">
         <v>16.34806277111788</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.921321314940013</v>
+        <v>6.857507714163971</v>
       </c>
       <c r="C2" t="n">
-        <v>5.753041546886309</v>
+        <v>7.415140410176159</v>
       </c>
       <c r="D2" t="n">
-        <v>11.06429662686155</v>
+        <v>13.82791641431632</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.28871594050657</v>
+        <v>10.05800523000857</v>
       </c>
       <c r="C3" t="n">
-        <v>11.3588209381356</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="D3" t="n">
-        <v>7.40237769002095</v>
+        <v>6.366633862040565</v>
       </c>
     </row>
     <row r="4">
@@ -4546,7 +4546,7 @@
         <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>19.73116535995239</v>
       </c>
     </row>
     <row r="5">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39957908843316</v>
+        <v>13.39983414221854</v>
       </c>
       <c r="C21" t="n">
-        <v>70.15073758062064</v>
+        <v>70.15207286220293</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57642106922743</v>
+        <v>1.576451075555122</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.158102438112742</v>
+        <v>6.022040417849935</v>
       </c>
       <c r="C2" t="n">
-        <v>9.573021864110649</v>
+        <v>5.847289326494002</v>
       </c>
       <c r="D2" t="n">
-        <v>18.87311786644068</v>
+        <v>13.85835059314797</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.41267819314893</v>
+        <v>18.18687622117216</v>
       </c>
       <c r="C3" t="n">
-        <v>18.40776945462769</v>
+        <v>22.31021657900877</v>
       </c>
       <c r="D3" t="n">
-        <v>14.90783888898781</v>
+        <v>16.43936530761284</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.04800782651686</v>
+        <v>11.77999070325748</v>
       </c>
       <c r="C4" t="n">
-        <v>18.13582534055133</v>
+        <v>17.1913840490659</v>
       </c>
       <c r="D4" t="n">
-        <v>18.95263943048468</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="5">
@@ -4871,7 +4871,7 @@
         <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.15790681613028</v>
       </c>
     </row>
     <row r="6">
@@ -4910,7 +4910,7 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
         <v>36.80081269369168</v>
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44601867536312</v>
+        <v>15.44581480064277</v>
       </c>
       <c r="C21" t="n">
-        <v>86.17252524149954</v>
+        <v>86.17138783516494</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251793405339605</v>
+        <v>3.251750484345846</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.005931543954486</v>
+        <v>5.020657759518188</v>
       </c>
       <c r="C2" t="n">
-        <v>7.445574589007809</v>
+        <v>9.924487542231006</v>
       </c>
       <c r="D2" t="n">
-        <v>25.48224341143021</v>
+        <v>20.53128973891355</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.10833640483242</v>
+        <v>19.94420461177396</v>
       </c>
       <c r="C3" t="n">
-        <v>29.83531273206057</v>
+        <v>22.58019719767664</v>
       </c>
       <c r="D3" t="n">
-        <v>26.54645792283375</v>
+        <v>23.70920705756047</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.32123678793373</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="C4" t="n">
-        <v>34.40829353844221</v>
+        <v>39.781398723785</v>
       </c>
       <c r="D4" t="n">
-        <v>22.16884490959723</v>
+        <v>22.56448923440869</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.99557428756428</v>
+        <v>10.77468105410875</v>
       </c>
       <c r="C5" t="n">
-        <v>21.69662426385451</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D5" t="n">
-        <v>29.28062527916113</v>
+        <v>29.13336312352411</v>
       </c>
     </row>
     <row r="6">
@@ -5196,7 +5196,7 @@
         <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.66925850132262</v>
       </c>
     </row>
     <row r="7">
@@ -5221,7 +5221,7 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="D8" t="n">
         <v>38.55323234577224</v>
@@ -5235,7 +5235,7 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
         <v>41.26874649571891</v>
@@ -5249,7 +5249,7 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74395782279209</v>
+        <v>16.74461037807792</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1381427190317</v>
+        <v>102.1421233062753</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023187346837627</v>
+        <v>5.023383113423377</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.518403845571321</v>
+        <v>6.089781009442965</v>
       </c>
       <c r="C2" t="n">
-        <v>6.391177554646736</v>
+        <v>7.917795234750526</v>
       </c>
       <c r="D2" t="n">
-        <v>28.78778793162922</v>
+        <v>23.6846633649543</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.58801012158161</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="C3" t="n">
-        <v>29.27571654063988</v>
+        <v>31.94607029619121</v>
       </c>
       <c r="D3" t="n">
-        <v>40.00621894805752</v>
+        <v>34.03719290623692</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.5029011709484</v>
+        <v>32.23863111205676</v>
       </c>
       <c r="C4" t="n">
-        <v>56.56437572788423</v>
+        <v>49.30238795957057</v>
       </c>
       <c r="D4" t="n">
-        <v>29.82647700272235</v>
+        <v>28.77993394999525</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.7645858396258</v>
+        <v>24.37188675792708</v>
       </c>
       <c r="C5" t="n">
-        <v>44.71860792844222</v>
+        <v>49.70097752749479</v>
       </c>
       <c r="D5" t="n">
-        <v>30.80233422074368</v>
+        <v>30.82687791334985</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.42517887139688</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>23.94973524510094</v>
+        <v>22.94344384824796</v>
       </c>
       <c r="D6" t="n">
         <v>38.07806645691679</v>
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5532,7 +5532,7 @@
         <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.79389940203295</v>
       </c>
       <c r="D8" t="n">
         <v>40.38910055271378</v>
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5577,7 +5577,7 @@
         <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5591,7 +5591,7 @@
         <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5675,7 +5675,7 @@
         <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>37.91411459030757</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07425855114096</v>
+        <v>18.07628933833449</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9130200717291</v>
+        <v>117.9262685405631</v>
       </c>
       <c r="D21" t="n">
-        <v>6.885431829006081</v>
+        <v>6.886205462222661</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.564366061221675</v>
+        <v>6.596362824834318</v>
       </c>
       <c r="C2" t="n">
-        <v>4.176354733865931</v>
+        <v>10.60091171045706</v>
       </c>
       <c r="D2" t="n">
-        <v>36.41694934133118</v>
+        <v>27.06678420608456</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.31173810606075</v>
+        <v>17.86780821729195</v>
       </c>
       <c r="C3" t="n">
-        <v>25.10328879759094</v>
+        <v>29.36898257254333</v>
       </c>
       <c r="D3" t="n">
-        <v>49.84333094461056</v>
+        <v>41.83226967795659</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.49616780573891</v>
+        <v>24.72138894063893</v>
       </c>
       <c r="C4" t="n">
-        <v>54.7393067456894</v>
+        <v>55.26257827205296</v>
       </c>
       <c r="D4" t="n">
-        <v>36.80768492762142</v>
+        <v>33.61700488881928</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.64753687864217</v>
+        <v>22.33476027161494</v>
       </c>
       <c r="C5" t="n">
-        <v>57.5304154688631</v>
+        <v>53.77523050011905</v>
       </c>
       <c r="D5" t="n">
-        <v>28.12707172667112</v>
+        <v>27.85709110800325</v>
       </c>
     </row>
     <row r="6">
@@ -5812,10 +5812,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.15600007398401</v>
+        <v>11.95474179461341</v>
       </c>
       <c r="C6" t="n">
-        <v>32.72459622565894</v>
+        <v>35.17994723398021</v>
       </c>
       <c r="D6" t="n">
         <v>30.59125846433062</v>
@@ -5829,10 +5829,10 @@
         <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>18.08575620763474</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5854,7 +5854,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
         <v>21.96562313481813</v>
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.065249387784838</v>
+        <v>7.066597301250319</v>
       </c>
       <c r="C21" t="n">
-        <v>66.23671301048284</v>
+        <v>66.24934969922174</v>
       </c>
       <c r="D21" t="n">
-        <v>5.298937040838628</v>
+        <v>5.299947975937739</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.69708192774424</v>
+        <v>6.56200165518568</v>
       </c>
       <c r="C2" t="n">
-        <v>3.82587080344982</v>
+        <v>6.017131679328701</v>
       </c>
       <c r="D2" t="n">
-        <v>29.75677291572082</v>
+        <v>29.73615621393164</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.56547098211294</v>
+        <v>21.13702807243383</v>
       </c>
       <c r="C3" t="n">
-        <v>19.6055016538088</v>
+        <v>37.28677780729386</v>
       </c>
       <c r="D3" t="n">
-        <v>69.84644041863933</v>
+        <v>55.13985980902211</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.95861203216817</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="C4" t="n">
-        <v>59.43598776280615</v>
+        <v>67.06809441562085</v>
       </c>
       <c r="D4" t="n">
-        <v>54.03735713715294</v>
+        <v>48.4600484293268</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.62423697564751</v>
+        <v>30.97414006898687</v>
       </c>
       <c r="C5" t="n">
-        <v>84.72482687649975</v>
+        <v>83.89034132788996</v>
       </c>
       <c r="D5" t="n">
-        <v>35.85833489761475</v>
+        <v>34.41025703385071</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.21891404251382</v>
+        <v>22.66168225712913</v>
       </c>
       <c r="C6" t="n">
-        <v>67.78378849201678</v>
+        <v>65.24793417194728</v>
       </c>
       <c r="D6" t="n">
-        <v>32.80509953740717</v>
+        <v>32.72459622565894</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.59992996275281</v>
+        <v>10.4801567428347</v>
       </c>
       <c r="C7" t="n">
-        <v>35.45287309576081</v>
+        <v>37.30935800449154</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>22.19731559302038</v>
+        <v>21.86352137357647</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.288431818849042</v>
+        <v>7.290608906027471</v>
       </c>
       <c r="C21" t="n">
-        <v>75.61748012055881</v>
+        <v>75.64006740003502</v>
       </c>
       <c r="D21" t="n">
-        <v>6.377377841492911</v>
+        <v>6.379282792774037</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.75853112248429</v>
+        <v>5.661739010391356</v>
       </c>
       <c r="C2" t="n">
-        <v>4.241150082346221</v>
+        <v>8.059166904162065</v>
       </c>
       <c r="D2" t="n">
-        <v>22.7598570275538</v>
+        <v>28.08092958457152</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.97013096271187</v>
+        <v>22.04514469886213</v>
       </c>
       <c r="C3" t="n">
-        <v>16.74370709592935</v>
+        <v>28.87319998189869</v>
       </c>
       <c r="D3" t="n">
-        <v>77.44516764950964</v>
+        <v>66.13543409658638</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.31819373382976</v>
+        <v>36.80768492762142</v>
       </c>
       <c r="C4" t="n">
-        <v>53.39922112939251</v>
+        <v>82.58756212435443</v>
       </c>
       <c r="D4" t="n">
-        <v>76.88262621497621</v>
+        <v>65.2047372729604</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.5518496874405</v>
+        <v>40.05530633326987</v>
       </c>
       <c r="C5" t="n">
-        <v>98.32203258031808</v>
+        <v>106.814150222053</v>
       </c>
       <c r="D5" t="n">
-        <v>46.82936549257286</v>
+        <v>43.73686022419541</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.91956310817655</v>
+        <v>33.08686112852601</v>
       </c>
       <c r="C6" t="n">
-        <v>105.2178284549477</v>
+        <v>102.0379476408923</v>
       </c>
       <c r="D6" t="n">
-        <v>37.07177506006381</v>
+        <v>36.58875518957439</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.28348840681585</v>
+        <v>19.52303484665207</v>
       </c>
       <c r="C7" t="n">
-        <v>70.00744704213579</v>
+        <v>68.86960145291374</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>35.33309987584271</v>
       </c>
     </row>
     <row r="8">
@@ -6465,10 +6465,10 @@
         <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>36.04977569994287</v>
+        <v>37.1346069131356</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -6493,7 +6493,7 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
         <v>34.30717352490479</v>
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6535,7 +6535,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
         <v>31.73990327829938</v>
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.499129506855982</v>
+        <v>7.500702444319757</v>
       </c>
       <c r="C21" t="n">
-        <v>85.30259814048679</v>
+        <v>85.32049030413724</v>
       </c>
       <c r="D21" t="n">
-        <v>7.499129506855982</v>
+        <v>7.500702444319757</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_50_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_50_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497648726365</v>
+        <v>10.84497636260664</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907248217278</v>
+        <v>37.78907204780826</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.907175936453058</v>
+        <v>4.435536127787089</v>
       </c>
       <c r="C2" t="n">
-        <v>7.384706231344508</v>
+        <v>8.322275288900212</v>
       </c>
       <c r="D2" t="n">
-        <v>30.55689729468197</v>
+        <v>27.06776595378881</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.51852701875834</v>
+        <v>15.87486037767093</v>
       </c>
       <c r="C3" t="n">
-        <v>30.15438073594078</v>
+        <v>20.2240027074843</v>
       </c>
       <c r="D3" t="n">
-        <v>72.27626598665017</v>
+        <v>52.72476045657496</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.52614432068083</v>
+        <v>31.75364774615883</v>
       </c>
       <c r="C4" t="n">
-        <v>76.16791388628454</v>
+        <v>62.46075243959057</v>
       </c>
       <c r="D4" t="n">
-        <v>81.030510265419</v>
+        <v>76.52527005063037</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.98291904506286</v>
+        <v>38.53359739168732</v>
       </c>
       <c r="C5" t="n">
-        <v>131.0387748243431</v>
+        <v>103.353489564583</v>
       </c>
       <c r="D5" t="n">
-        <v>56.49958037940395</v>
+        <v>63.83814446864886</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.51203999992289</v>
+        <v>36.54850353370026</v>
       </c>
       <c r="C6" t="n">
-        <v>136.734875004383</v>
+        <v>145.1072194261998</v>
       </c>
       <c r="D6" t="n">
-        <v>41.45920555034281</v>
+        <v>46.28940425523712</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.64387192973244</v>
+        <v>24.852943133008</v>
       </c>
       <c r="C7" t="n">
-        <v>107.9755577561769</v>
+        <v>147.6204935490717</v>
       </c>
       <c r="D7" t="n">
-        <v>38.14777054391831</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.77039421039326</v>
+        <v>12.68418033886879</v>
       </c>
       <c r="C8" t="n">
-        <v>64.75607857211961</v>
+        <v>102.9755166984479</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
-        <v>36.49843440078366</v>
+        <v>54.91405783704532</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
         <v>32.00006641992479</v>
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.695380667605328</v>
+        <v>7.667469851350821</v>
       </c>
       <c r="C21" t="n">
-        <v>94.26841317816526</v>
+        <v>93.92650567904755</v>
       </c>
       <c r="D21" t="n">
-        <v>8.657303251055994</v>
+        <v>7.667469851350821</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.219371706403543</v>
+        <v>4.820381227851839</v>
       </c>
       <c r="C2" t="n">
-        <v>6.089781009442965</v>
+        <v>5.463425974133499</v>
       </c>
       <c r="D2" t="n">
-        <v>30.12591005251763</v>
+        <v>25.71000887881547</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.99820073550753</v>
+        <v>15.2514505854742</v>
       </c>
       <c r="C3" t="n">
-        <v>29.23644663247001</v>
+        <v>26.21266370338984</v>
       </c>
       <c r="D3" t="n">
-        <v>78.36801049150165</v>
+        <v>60.41675371934871</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.83695743229957</v>
+        <v>30.64329109265569</v>
       </c>
       <c r="C4" t="n">
-        <v>74.89164187076368</v>
+        <v>55.91347699996859</v>
       </c>
       <c r="D4" t="n">
-        <v>96.00118100747861</v>
+        <v>84.08080038251383</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.94074495150926</v>
+        <v>42.5096755938869</v>
       </c>
       <c r="C5" t="n">
-        <v>135.4075521082413</v>
+        <v>108.9249077861836</v>
       </c>
       <c r="D5" t="n">
-        <v>69.48319376806802</v>
+        <v>74.07286428542186</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.65545728020094</v>
+        <v>44.03531152628644</v>
       </c>
       <c r="C6" t="n">
-        <v>168.5739348008113</v>
+        <v>153.0367956334013</v>
       </c>
       <c r="D6" t="n">
-        <v>48.74475526355839</v>
+        <v>54.6214970211798</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.64493579289469</v>
+        <v>33.23706852727577</v>
       </c>
       <c r="C7" t="n">
-        <v>148.9379989681709</v>
+        <v>177.6236851385584</v>
       </c>
       <c r="D7" t="n">
-        <v>40.8426679920758</v>
+        <v>42.99858595060179</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.5311098124643</v>
+        <v>19.10971906316416</v>
       </c>
       <c r="C8" t="n">
-        <v>101.6403398206723</v>
+        <v>145.2004854581033</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>9.651561680450389</v>
       </c>
       <c r="C9" t="n">
-        <v>56.46718270516377</v>
+        <v>88.08436752043229</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>36.30012136452581</v>
+        <v>47.68839473378882</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>31.8076438698924</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.873737902204783</v>
+        <v>7.845309818955996</v>
       </c>
       <c r="C21" t="n">
-        <v>102.3585927286622</v>
+        <v>101.989027646428</v>
       </c>
       <c r="D21" t="n">
-        <v>9.842172377755979</v>
+        <v>8.825973546325494</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.822565707438585</v>
+        <v>6.162430339557228</v>
       </c>
       <c r="C2" t="n">
-        <v>8.430267536367362</v>
+        <v>6.915430828714532</v>
       </c>
       <c r="D2" t="n">
-        <v>30.98003055521235</v>
+        <v>35.09158994059799</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.18473279931442</v>
+        <v>15.37907778702628</v>
       </c>
       <c r="C3" t="n">
-        <v>26.3942870286755</v>
+        <v>23.6699371493906</v>
       </c>
       <c r="D3" t="n">
-        <v>82.02011195129978</v>
+        <v>64.72171740247097</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.56068541677872</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="C4" t="n">
-        <v>73.09209832887927</v>
+        <v>59.49980136358219</v>
       </c>
       <c r="D4" t="n">
-        <v>107.6663072293392</v>
+        <v>91.22792366943061</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.68334712654735</v>
+        <v>44.10501561328796</v>
       </c>
       <c r="C5" t="n">
-        <v>136.217493964245</v>
+        <v>105.0224606618026</v>
       </c>
       <c r="D5" t="n">
-        <v>83.9394287131023</v>
+        <v>84.4303025652257</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.78000036992004</v>
+        <v>49.3887817575443</v>
       </c>
       <c r="C6" t="n">
-        <v>186.9689415352838</v>
+        <v>162.2141731727005</v>
       </c>
       <c r="D6" t="n">
-        <v>56.39256987964104</v>
+        <v>62.34981494901069</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.58611304609789</v>
+        <v>41.14210104187108</v>
       </c>
       <c r="C7" t="n">
-        <v>188.3433883212293</v>
+        <v>195.8891011760703</v>
       </c>
       <c r="D7" t="n">
-        <v>44.73529763941441</v>
+        <v>47.37030847761284</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31.12631096314512</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="C8" t="n">
-        <v>143.0308230317178</v>
+        <v>185.1723432365121</v>
       </c>
       <c r="D8" t="n">
-        <v>39.72151211382594</v>
+        <v>40.80634332701867</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.53124868118453</v>
+        <v>13.64531134132641</v>
       </c>
       <c r="C9" t="n">
-        <v>85.08905527477528</v>
+        <v>126.2468642799143</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>49.25428232206248</v>
+        <v>70.89200172366218</v>
       </c>
       <c r="D10" t="n">
         <v>36.15776794741003</v>
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>36.07235589714055</v>
+        <v>42.46942393801276</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.035898133354854</v>
+        <v>8.008508305610254</v>
       </c>
       <c r="C21" t="n">
-        <v>110.4935993336292</v>
+        <v>110.116989202141</v>
       </c>
       <c r="D21" t="n">
-        <v>11.04935993336292</v>
+        <v>10.01063538201282</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.161849502480481</v>
+        <v>5.617560363700249</v>
       </c>
       <c r="C2" t="n">
-        <v>5.799183688985909</v>
+        <v>4.701589755637975</v>
       </c>
       <c r="D2" t="n">
-        <v>25.57060070481242</v>
+        <v>28.69452189972577</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.02965771977243</v>
+        <v>19.28643364992859</v>
       </c>
       <c r="C3" t="n">
-        <v>41.6604638297134</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D3" t="n">
-        <v>87.52280783360315</v>
+        <v>69.80226177194821</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.26567807941916</v>
+        <v>21.18611545764617</v>
       </c>
       <c r="C4" t="n">
-        <v>107.9853752332194</v>
+        <v>84.97419079337843</v>
       </c>
       <c r="D4" t="n">
-        <v>100.4426076214912</v>
+        <v>89.88783805313372</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.23845118560752</v>
+        <v>27.80800372279091</v>
       </c>
       <c r="C5" t="n">
-        <v>111.722888743287</v>
+        <v>96.92304210176638</v>
       </c>
       <c r="D5" t="n">
-        <v>56.25414345334224</v>
+        <v>59.93569734426779</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.79251674370121</v>
+        <v>25.51954982419159</v>
       </c>
       <c r="C6" t="n">
-        <v>124.0556034040355</v>
+        <v>129.0065570765522</v>
       </c>
       <c r="D6" t="n">
-        <v>29.46421209985528</v>
+        <v>31.19503330244241</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.60099382591507</v>
+        <v>17.30723027816702</v>
       </c>
       <c r="C7" t="n">
-        <v>100.5496181212541</v>
+        <v>130.1934900509865</v>
       </c>
       <c r="D7" t="n">
-        <v>27.90716024091983</v>
+        <v>28.68568617038755</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="C8" t="n">
-        <v>62.66986470059513</v>
+        <v>93.04513866999145</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>26.70353755551324</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>37.60780930658255</v>
+        <v>54.1374954029861</v>
       </c>
       <c r="D9" t="n">
         <v>27.5124976638126</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>28.18597658892593</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1971,7 +1971,7 @@
         <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.496404485450391</v>
+        <v>3.461642405174254</v>
       </c>
       <c r="C2" t="n">
-        <v>2.675262494072558</v>
+        <v>2.187333885061894</v>
       </c>
       <c r="D2" t="n">
-        <v>18.71898347687393</v>
+        <v>19.94322286406971</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.53034904893831</v>
+        <v>19.83130362578557</v>
       </c>
       <c r="C3" t="n">
-        <v>32.62347621212151</v>
+        <v>27.71473769088746</v>
       </c>
       <c r="D3" t="n">
-        <v>88.80398858764524</v>
+        <v>75.80074024489623</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.63351467334223</v>
+        <v>28.05245890114836</v>
       </c>
       <c r="C4" t="n">
-        <v>108.9936301254809</v>
+        <v>90.0027025345306</v>
       </c>
       <c r="D4" t="n">
-        <v>116.651262218606</v>
+        <v>102.944100771912</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.26361677301944</v>
+        <v>31.02322745419922</v>
       </c>
       <c r="C5" t="n">
-        <v>154.3552828002048</v>
+        <v>126.9890655443249</v>
       </c>
       <c r="D5" t="n">
-        <v>72.69841749947632</v>
+        <v>73.33655350723674</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.58875518957439</v>
+        <v>30.22899356146354</v>
       </c>
       <c r="C6" t="n">
-        <v>152.0707558924225</v>
+        <v>147.200305531654</v>
       </c>
       <c r="D6" t="n">
-        <v>35.98498035146259</v>
+        <v>38.15856976866503</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.3433750167749</v>
+        <v>16.34904451882213</v>
       </c>
       <c r="C7" t="n">
-        <v>130.6126963206999</v>
+        <v>156.663371652889</v>
       </c>
       <c r="D7" t="n">
-        <v>30.3625112492411</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>85.11752595819846</v>
+        <v>121.8348900970292</v>
       </c>
       <c r="D8" t="n">
-        <v>28.45595720759379</v>
+        <v>27.87181732356695</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>42.3781214015178</v>
+        <v>59.46249495082079</v>
       </c>
       <c r="D9" t="n">
         <v>28.39999758845172</v>
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>34.87658719336794</v>
       </c>
       <c r="D10" t="n">
         <v>29.75186417719959</v>
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2170,7 +2170,7 @@
         <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2268,7 +2268,7 @@
         <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.499750639190632</v>
+        <v>3.413536767666159</v>
       </c>
       <c r="C2" t="n">
-        <v>3.372303364087794</v>
+        <v>8.591274159863838</v>
       </c>
       <c r="D2" t="n">
-        <v>19.4965276586374</v>
+        <v>20.63830023867645</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.38599107868502</v>
+        <v>15.75214191464007</v>
       </c>
       <c r="C3" t="n">
-        <v>20.90631736193583</v>
+        <v>17.31802950291373</v>
       </c>
       <c r="D3" t="n">
-        <v>83.48782476914876</v>
+        <v>74.75517893987337</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.69580674706629</v>
+        <v>33.02991976167969</v>
       </c>
       <c r="C4" t="n">
-        <v>94.89082435397546</v>
+        <v>80.03501809331273</v>
       </c>
       <c r="D4" t="n">
-        <v>131.7367974420625</v>
+        <v>115.1707866806018</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.38128762880881</v>
+        <v>36.25103397931348</v>
       </c>
       <c r="C5" t="n">
-        <v>178.604451095101</v>
+        <v>146.0104273141069</v>
       </c>
       <c r="D5" t="n">
-        <v>93.7569057555704</v>
+        <v>89.53539062730911</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.83405324691584</v>
+        <v>35.62271544859552</v>
       </c>
       <c r="C6" t="n">
-        <v>195.2205309894783</v>
+        <v>174.7324381495516</v>
       </c>
       <c r="D6" t="n">
-        <v>47.45670227558657</v>
+        <v>50.59633143376788</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.7455727803466</v>
+        <v>24.43373686329462</v>
       </c>
       <c r="C7" t="n">
-        <v>173.0723027816702</v>
+        <v>183.4326863045868</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>34.43480072645687</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.51866588747858</v>
+        <v>11.59934912567606</v>
       </c>
       <c r="C8" t="n">
-        <v>124.8390380720244</v>
+        <v>162.6412334240478</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>69.11405663127118</v>
+        <v>99.7328040313207</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>39.71660337530471</v>
+        <v>49.39663573917827</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2481,7 +2481,7 @@
         <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.246639657944202</v>
+        <v>2.02534551386117</v>
       </c>
       <c r="C2" t="n">
-        <v>1.621847207415731</v>
+        <v>3.942698780255191</v>
       </c>
       <c r="D2" t="n">
-        <v>13.65022007984765</v>
+        <v>14.22454248683204</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.49045724596268</v>
+        <v>15.4968875115359</v>
       </c>
       <c r="C3" t="n">
-        <v>18.90846078379357</v>
+        <v>25.57943643415064</v>
       </c>
       <c r="D3" t="n">
-        <v>83.07058199484386</v>
+        <v>76.14435194138262</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.7543517564226</v>
+        <v>36.50137964389641</v>
       </c>
       <c r="C4" t="n">
-        <v>88.79024411978578</v>
+        <v>75.05755723278139</v>
       </c>
       <c r="D4" t="n">
-        <v>141.8959226856085</v>
+        <v>126.3509295365645</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.36932672990861</v>
+        <v>38.01817984695774</v>
       </c>
       <c r="C5" t="n">
-        <v>208.4250376115979</v>
+        <v>169.4741974456057</v>
       </c>
       <c r="D5" t="n">
-        <v>99.50012982541426</v>
+        <v>94.78774084502956</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.66296710446964</v>
+        <v>29.62521872335175</v>
       </c>
       <c r="C6" t="n">
-        <v>231.4872729320597</v>
+        <v>215.1048489912932</v>
       </c>
       <c r="D6" t="n">
-        <v>46.85292743747478</v>
+        <v>49.79129831628549</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.92310488389926</v>
+        <v>7.665486074759095</v>
       </c>
       <c r="C7" t="n">
-        <v>174.2101483708923</v>
+        <v>199.9613906532861</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>34.43480072645687</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>88.8727109269425</v>
+        <v>124.5052438525805</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>30.28593492830985</v>
+        <v>37.71874679716245</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2778,7 +2778,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.69038962026376</v>
+        <v>2.146100481483527</v>
       </c>
       <c r="C2" t="n">
-        <v>8.970228773703107</v>
+        <v>5.127668259281091</v>
       </c>
       <c r="D2" t="n">
-        <v>19.41798784229766</v>
+        <v>12.61840324268425</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.49336143134641</v>
+        <v>11.32445976848696</v>
       </c>
       <c r="C3" t="n">
-        <v>12.4976482750619</v>
+        <v>20.31726873938774</v>
       </c>
       <c r="D3" t="n">
-        <v>76.26707040441346</v>
+        <v>70.34222300928397</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.5081130091059</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="C4" t="n">
-        <v>68.29331555052087</v>
+        <v>70.10562181256049</v>
       </c>
       <c r="D4" t="n">
-        <v>148.9537069314388</v>
+        <v>134.1872397118625</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.74501730546565</v>
+        <v>45.40583132141499</v>
       </c>
       <c r="C5" t="n">
-        <v>189.0846078379357</v>
+        <v>154.6007197262665</v>
       </c>
       <c r="D5" t="n">
-        <v>121.4176473227243</v>
+        <v>115.5762484824558</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.01393406097126</v>
+        <v>38.11831811279092</v>
       </c>
       <c r="C6" t="n">
-        <v>278.2194454019121</v>
+        <v>244.408054467652</v>
       </c>
       <c r="D6" t="n">
-        <v>61.86679507852126</v>
+        <v>63.31585468998956</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.70269467652924</v>
+        <v>16.88802400845363</v>
       </c>
       <c r="C7" t="n">
-        <v>245.8944204918816</v>
+        <v>250.0265965790564</v>
       </c>
       <c r="D7" t="n">
-        <v>38.14777054391831</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>146.368765226157</v>
+        <v>185.506137455956</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>32.62838495064274</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>59.57343244140068</v>
+        <v>79.76405572694058</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.16670148773948</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>12.18348900970292</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.670353755551324</v>
+        <v>1.515818455357075</v>
       </c>
       <c r="C2" t="n">
-        <v>4.955862411037899</v>
+        <v>3.865140711619692</v>
       </c>
       <c r="D2" t="n">
-        <v>14.12047723018187</v>
+        <v>9.012443924985719</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.00110492089126</v>
+        <v>9.743845964649594</v>
       </c>
       <c r="C3" t="n">
-        <v>23.10052348092745</v>
+        <v>20.54797944988574</v>
       </c>
       <c r="D3" t="n">
-        <v>74.61282552275759</v>
+        <v>65.64456024446297</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.87073776487146</v>
+        <v>29.82647700272235</v>
       </c>
       <c r="C4" t="n">
-        <v>54.39471330149878</v>
+        <v>63.53282093262809</v>
       </c>
       <c r="D4" t="n">
-        <v>153.9056423516597</v>
+        <v>137.9394794374938</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.28560043760715</v>
+        <v>48.74377351585415</v>
       </c>
       <c r="C5" t="n">
-        <v>170.0632460681537</v>
+        <v>148.612058730361</v>
       </c>
       <c r="D5" t="n">
-        <v>136.3156687346697</v>
+        <v>130.6706194352505</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.58753676215866</v>
+        <v>45.2026095466359</v>
       </c>
       <c r="C6" t="n">
-        <v>299.7138296386918</v>
+        <v>257.5300942826149</v>
       </c>
       <c r="D6" t="n">
-        <v>74.78757661411353</v>
+        <v>74.66682164649117</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.72643654788041</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="C7" t="n">
-        <v>303.8047723222882</v>
+        <v>296.019513027611</v>
       </c>
       <c r="D7" t="n">
-        <v>42.22006002113408</v>
+        <v>43.89688509998763</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>193.600647277471</v>
+        <v>231.2359455197725</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>34.54770171244525</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>68.11561921605218</v>
+        <v>94.96249193638545</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>11.36962016288231</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.765403356414017</v>
+        <v>2.695879195861741</v>
       </c>
       <c r="C2" t="n">
-        <v>8.553967747102458</v>
+        <v>6.645450210046659</v>
       </c>
       <c r="D2" t="n">
-        <v>13.70814319439821</v>
+        <v>10.41339789894592</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.12949288596934</v>
+        <v>7.530004891573036</v>
       </c>
       <c r="C3" t="n">
-        <v>21.13702807243383</v>
+        <v>17.96107424919539</v>
       </c>
       <c r="D3" t="n">
-        <v>69.35556656651592</v>
+        <v>58.96867585558466</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.71459882216722</v>
+        <v>24.74691438094935</v>
       </c>
       <c r="C4" t="n">
-        <v>55.64545987670921</v>
+        <v>57.84064774340508</v>
       </c>
       <c r="D4" t="n">
-        <v>154.9904735648525</v>
+        <v>138.4499882437022</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.62292073724056</v>
+        <v>47.22206457427158</v>
       </c>
       <c r="C5" t="n">
-        <v>140.119941088626</v>
+        <v>134.5976102522377</v>
       </c>
       <c r="D5" t="n">
-        <v>153.6189720220197</v>
+        <v>143.5315143608837</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.73095404243671</v>
+        <v>53.25294072145974</v>
       </c>
       <c r="C6" t="n">
-        <v>289.1678957996726</v>
+        <v>249.8420280106581</v>
       </c>
       <c r="D6" t="n">
-        <v>92.37755023110364</v>
+        <v>92.45805354285189</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.65627479698915</v>
+        <v>28.86534600026472</v>
       </c>
       <c r="C7" t="n">
-        <v>356.564875696216</v>
+        <v>329.1966949449277</v>
       </c>
       <c r="D7" t="n">
-        <v>49.88554609589318</v>
+        <v>51.98157744446011</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>276.465062254423</v>
+        <v>299.0796206217483</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>37.30150402285756</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>129.9078014690506</v>
+        <v>166.6281108509941</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>33.61405964570653</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>47.97310156802039</v>
+        <v>61.35432277690443</v>
       </c>
       <c r="D10" t="n">
-        <v>26.1930287493049</v>
+        <v>26.76244241776806</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
         <v>11.67690719431156</v>
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.732023934469626</v>
+        <v>4.337361357362409</v>
       </c>
       <c r="C2" t="n">
-        <v>4.200898426472102</v>
+        <v>13.06509844811655</v>
       </c>
       <c r="D2" t="n">
-        <v>3.717878555982671</v>
+        <v>10.36823750455056</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.406664533736432</v>
+        <v>1.906554041647306</v>
       </c>
       <c r="C2" t="n">
-        <v>4.927391727614741</v>
+        <v>3.721805546799658</v>
       </c>
       <c r="D2" t="n">
-        <v>10.08843940884022</v>
+        <v>7.663522579350602</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.75352457297182</v>
+        <v>10.70595871481147</v>
       </c>
       <c r="C3" t="n">
-        <v>27.84236489243954</v>
+        <v>23.14470212761856</v>
       </c>
       <c r="D3" t="n">
-        <v>74.97116343480768</v>
+        <v>63.51907646476863</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.58392856651115</v>
+        <v>35.05919226635785</v>
       </c>
       <c r="C4" t="n">
-        <v>81.77074803442109</v>
+        <v>81.73245987395545</v>
       </c>
       <c r="D4" t="n">
-        <v>157.5430175958942</v>
+        <v>140.7983287522605</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.7054032399305</v>
+        <v>31.73499453977815</v>
       </c>
       <c r="C5" t="n">
-        <v>228.3545160078081</v>
+        <v>207.0996782108647</v>
       </c>
       <c r="D5" t="n">
-        <v>138.2055330653448</v>
+        <v>132.3395905324701</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.89060939866788</v>
+        <v>17.91198686398306</v>
       </c>
       <c r="C6" t="n">
-        <v>291.5024918403715</v>
+        <v>268.2370347451306</v>
       </c>
       <c r="D6" t="n">
-        <v>73.82153687313468</v>
+        <v>75.06933820523237</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.928774385946488</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>194.3919359270939</v>
+        <v>210.3217741762027</v>
       </c>
       <c r="D7" t="n">
-        <v>31.91956310817654</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>95.71549242554278</v>
+        <v>122.7528242004999</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>24.70077223884975</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>36.60937189136354</v>
+        <v>46.81562102471339</v>
       </c>
       <c r="D9" t="n">
-        <v>19.96874830438012</v>
+        <v>20.41249826669968</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.17036643664921</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
         <v>9.626036240139976</v>
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.857507714163971</v>
+        <v>5.985715752792803</v>
       </c>
       <c r="C2" t="n">
-        <v>7.415140410176159</v>
+        <v>6.635632733004192</v>
       </c>
       <c r="D2" t="n">
-        <v>13.82791641431632</v>
+        <v>14.08906130364598</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.05800523000857</v>
+        <v>9.21861094287755</v>
       </c>
       <c r="C3" t="n">
-        <v>10.75013736150257</v>
+        <v>32.92290926191679</v>
       </c>
       <c r="D3" t="n">
-        <v>6.366633862040565</v>
+        <v>11.84478605173777</v>
       </c>
     </row>
     <row r="4">
@@ -4543,10 +4543,10 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
-        <v>19.73116535995239</v>
+        <v>19.62906359871073</v>
       </c>
     </row>
     <row r="5">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39983414221854</v>
+        <v>13.39723522623283</v>
       </c>
       <c r="C21" t="n">
-        <v>70.15207286220293</v>
+        <v>70.13846677263071</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576451075555122</v>
+        <v>1.576145320733274</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.022040417849935</v>
+        <v>4.255876297909923</v>
       </c>
       <c r="C2" t="n">
-        <v>5.847289326494002</v>
+        <v>6.764241682260523</v>
       </c>
       <c r="D2" t="n">
-        <v>13.85835059314797</v>
+        <v>24.6241959179185</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.18687622117216</v>
+        <v>16.05648370295658</v>
       </c>
       <c r="C3" t="n">
-        <v>22.31021657900877</v>
+        <v>28.51486206984861</v>
       </c>
       <c r="D3" t="n">
-        <v>16.43936530761284</v>
+        <v>20.81305133003238</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.77999070325748</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C4" t="n">
-        <v>17.1913840490659</v>
+        <v>50.70628717664351</v>
       </c>
       <c r="D4" t="n">
-        <v>18.48041878474196</v>
+        <v>21.27545449873262</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.15790681613028</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44581480064277</v>
+        <v>15.43803786579395</v>
       </c>
       <c r="C21" t="n">
-        <v>86.17138783516494</v>
+        <v>86.12800072495571</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251750484345846</v>
+        <v>3.250113234903989</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.020657759518188</v>
+        <v>5.4172838320339</v>
       </c>
       <c r="C2" t="n">
-        <v>9.924487542231006</v>
+        <v>7.563384313517426</v>
       </c>
       <c r="D2" t="n">
-        <v>20.53128973891355</v>
+        <v>19.75669080026281</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.94420461177396</v>
+        <v>15.45270886484479</v>
       </c>
       <c r="C3" t="n">
-        <v>22.58019719767664</v>
+        <v>27.18950266911541</v>
       </c>
       <c r="D3" t="n">
-        <v>23.70920705756047</v>
+        <v>35.68162031085032</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.95111790343269</v>
+        <v>21.96464138711389</v>
       </c>
       <c r="C4" t="n">
-        <v>39.781398723785</v>
+        <v>62.2054980364864</v>
       </c>
       <c r="D4" t="n">
-        <v>22.56448923440869</v>
+        <v>26.92933952749001</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.77468105410875</v>
+        <v>9.891108120286615</v>
       </c>
       <c r="C5" t="n">
-        <v>20.66578917439536</v>
+        <v>55.73872590861267</v>
       </c>
       <c r="D5" t="n">
-        <v>29.13336312352411</v>
+        <v>30.31146036862028</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.66925850132262</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.6242369756475</v>
+        <v>29.45733986592554</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74461037807792</v>
+        <v>16.72590788485543</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1421233062753</v>
+        <v>102.0280380976181</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023383113423377</v>
+        <v>4.181476971213858</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.089781009442965</v>
+        <v>4.785038310498954</v>
       </c>
       <c r="C2" t="n">
-        <v>7.917795234750526</v>
+        <v>5.911102927270045</v>
       </c>
       <c r="D2" t="n">
-        <v>23.6846633649543</v>
+        <v>18.7454906648886</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.44213062427633</v>
+        <v>17.07259257685203</v>
       </c>
       <c r="C3" t="n">
-        <v>31.94607029619121</v>
+        <v>28.38232612977529</v>
       </c>
       <c r="D3" t="n">
-        <v>34.03719290623692</v>
+        <v>42.76002125846983</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.23863111205676</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="C4" t="n">
-        <v>49.30238795957057</v>
+        <v>64.78356750783853</v>
       </c>
       <c r="D4" t="n">
-        <v>28.77993394999525</v>
+        <v>38.10948238345269</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.37188675792708</v>
+        <v>21.40209995258047</v>
       </c>
       <c r="C5" t="n">
-        <v>49.70097752749479</v>
+        <v>87.69461368184635</v>
       </c>
       <c r="D5" t="n">
-        <v>30.82687791334985</v>
+        <v>32.79037332184348</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.2641722479004</v>
+        <v>9.579894098040377</v>
       </c>
       <c r="C6" t="n">
-        <v>22.94344384824796</v>
+        <v>51.64287448649497</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>38.27932473628739</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.79389940203295</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5599,10 +5599,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5613,7 +5613,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
         <v>30.72870314292517</v>
@@ -5633,7 +5633,7 @@
         <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.91411459030757</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07628933833449</v>
+        <v>18.04309204609487</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9262685405631</v>
+        <v>117.7096957292856</v>
       </c>
       <c r="D21" t="n">
-        <v>6.886205462222661</v>
+        <v>6.014364015364956</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.596362824834318</v>
+        <v>4.995132319207771</v>
       </c>
       <c r="C2" t="n">
-        <v>10.60091171045706</v>
+        <v>5.746169312956581</v>
       </c>
       <c r="D2" t="n">
-        <v>27.06678420608456</v>
+        <v>17.15309588860027</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.86780821729195</v>
+        <v>14.78021168743573</v>
       </c>
       <c r="C3" t="n">
-        <v>29.36898257254333</v>
+        <v>23.74847696573034</v>
       </c>
       <c r="D3" t="n">
-        <v>41.83226967795659</v>
+        <v>44.68424675879358</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.72138894063893</v>
+        <v>21.51794618168159</v>
       </c>
       <c r="C4" t="n">
-        <v>55.26257827205296</v>
+        <v>56.98554549300611</v>
       </c>
       <c r="D4" t="n">
-        <v>33.61700488881928</v>
+        <v>43.86546917345174</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.33476027161494</v>
+        <v>18.4077694546277</v>
       </c>
       <c r="C5" t="n">
-        <v>53.77523050011905</v>
+        <v>76.96902001294994</v>
       </c>
       <c r="D5" t="n">
-        <v>27.85709110800325</v>
+        <v>31.14594591723007</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.95474179461341</v>
+        <v>10.50568218314512</v>
       </c>
       <c r="C6" t="n">
-        <v>35.17994723398021</v>
+        <v>65.44919245131787</v>
       </c>
       <c r="D6" t="n">
-        <v>30.59125846433062</v>
+        <v>31.11452999069417</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.270021676396877</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>17.66654993792135</v>
+        <v>30.30262463928205</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.066597301250319</v>
+        <v>7.048254877495123</v>
       </c>
       <c r="C21" t="n">
-        <v>66.24934969922174</v>
+        <v>66.07738947651677</v>
       </c>
       <c r="D21" t="n">
-        <v>5.299947975937739</v>
+        <v>4.405159298434452</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.56200165518568</v>
+        <v>5.283766144256333</v>
       </c>
       <c r="C2" t="n">
-        <v>6.017131679328701</v>
+        <v>7.456373813754525</v>
       </c>
       <c r="D2" t="n">
-        <v>29.73615621393164</v>
+        <v>17.26305163147591</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.13702807243383</v>
+        <v>16.42954783057037</v>
       </c>
       <c r="C3" t="n">
-        <v>37.28677780729386</v>
+        <v>22.91399141712056</v>
       </c>
       <c r="D3" t="n">
-        <v>55.13985980902211</v>
+        <v>48.29707831042184</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.29418982057133</v>
+        <v>25.99766095615978</v>
       </c>
       <c r="C4" t="n">
-        <v>67.06809441562085</v>
+        <v>58.67022455349363</v>
       </c>
       <c r="D4" t="n">
-        <v>48.4600484293268</v>
+        <v>56.6792402092811</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.97414006898687</v>
+        <v>26.65445017030091</v>
       </c>
       <c r="C5" t="n">
-        <v>83.89034132788996</v>
+        <v>94.46867284114934</v>
       </c>
       <c r="D5" t="n">
-        <v>34.41025703385071</v>
+        <v>40.91433557448583</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.66168225712913</v>
+        <v>18.79752329321368</v>
       </c>
       <c r="C6" t="n">
-        <v>65.24793417194728</v>
+        <v>99.05932510620744</v>
       </c>
       <c r="D6" t="n">
-        <v>32.72459622565894</v>
+        <v>34.49566908412018</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.4801567428347</v>
+        <v>9.282424543653592</v>
       </c>
       <c r="C7" t="n">
-        <v>37.30935800449154</v>
+        <v>67.73175586369169</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>21.86352137357647</v>
+        <v>31.2097595180061</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.34243432679967</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,7 +6238,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.290608906027471</v>
+        <v>7.267728253829283</v>
       </c>
       <c r="C21" t="n">
-        <v>75.64006740003502</v>
+        <v>75.40268063347881</v>
       </c>
       <c r="D21" t="n">
-        <v>6.379282792774037</v>
+        <v>5.450796190371962</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.661739010391356</v>
+        <v>4.230350857599506</v>
       </c>
       <c r="C2" t="n">
-        <v>8.059166904162065</v>
+        <v>3.937790041733956</v>
       </c>
       <c r="D2" t="n">
-        <v>28.08092958457152</v>
+        <v>17.58408313076462</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.04514469886213</v>
+        <v>17.63218876827272</v>
       </c>
       <c r="C3" t="n">
-        <v>28.87319998189869</v>
+        <v>26.53664044579129</v>
       </c>
       <c r="D3" t="n">
-        <v>66.13543409658638</v>
+        <v>50.89870972667589</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.80768492762142</v>
+        <v>29.20110371511713</v>
       </c>
       <c r="C4" t="n">
-        <v>82.58756212435443</v>
+        <v>57.94274950464675</v>
       </c>
       <c r="D4" t="n">
-        <v>65.2047372729604</v>
+        <v>68.17845106912399</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.05530633326987</v>
+        <v>33.55122779263475</v>
       </c>
       <c r="C5" t="n">
-        <v>106.814150222053</v>
+        <v>101.4636252339079</v>
       </c>
       <c r="D5" t="n">
-        <v>43.73686022419541</v>
+        <v>51.68901662859458</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.08686112852601</v>
+        <v>27.89439752076462</v>
       </c>
       <c r="C6" t="n">
-        <v>102.0379476408923</v>
+        <v>127.3964908415874</v>
       </c>
       <c r="D6" t="n">
-        <v>36.58875518957439</v>
+        <v>39.92964262712628</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.52303484665207</v>
+        <v>16.28915790886308</v>
       </c>
       <c r="C7" t="n">
-        <v>68.86960145291374</v>
+        <v>109.0535167354399</v>
       </c>
       <c r="D7" t="n">
-        <v>35.33309987584271</v>
+        <v>35.99185258539232</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>37.1346069131356</v>
+        <v>62.4195190360122</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>33.62976760897448</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>26.07031028627404</v>
+        <v>32.06093477758807</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
         <v>35.89465956267188</v>
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.500702444319757</v>
+        <v>7.474467557359437</v>
       </c>
       <c r="C21" t="n">
-        <v>85.32049030413724</v>
+        <v>85.0220684649636</v>
       </c>
       <c r="D21" t="n">
-        <v>7.500702444319757</v>
+        <v>6.540159112689508</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_50_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_50_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497636260664</v>
+        <v>10.84497650976441</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907204780826</v>
+        <v>37.78907256057613</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.435536127787089</v>
+        <v>0.8570657458074655</v>
       </c>
       <c r="C2" t="n">
-        <v>8.322275288900212</v>
+        <v>2.056761440397068</v>
       </c>
       <c r="D2" t="n">
-        <v>27.06776595378881</v>
+        <v>15.87976911619216</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.87486037767093</v>
+        <v>9.125344910974103</v>
       </c>
       <c r="C3" t="n">
-        <v>20.2240027074843</v>
+        <v>20.17982406079319</v>
       </c>
       <c r="D3" t="n">
-        <v>52.72476045657496</v>
+        <v>76.66467822463342</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.75364774615883</v>
+        <v>17.90609637775757</v>
       </c>
       <c r="C4" t="n">
-        <v>62.46075243959057</v>
+        <v>71.15216486528757</v>
       </c>
       <c r="D4" t="n">
-        <v>76.52527005063037</v>
+        <v>91.10029646787852</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.53359739168732</v>
+        <v>14.97165248976386</v>
       </c>
       <c r="C5" t="n">
-        <v>103.353489564583</v>
+        <v>77.28808801683016</v>
       </c>
       <c r="D5" t="n">
-        <v>63.83814446864886</v>
+        <v>52.76893910326607</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.54850353370026</v>
+        <v>10.34467555964864</v>
       </c>
       <c r="C6" t="n">
-        <v>145.1072194261998</v>
+        <v>49.3887817575443</v>
       </c>
       <c r="D6" t="n">
-        <v>46.28940425523712</v>
+        <v>30.99377502307181</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.852943133008</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>147.6204935490717</v>
+        <v>29.70375853969149</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>29.88341836956866</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.68418033886879</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>102.9755166984479</v>
+        <v>27.53802310412303</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>30.87596529856218</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>54.91405783704532</v>
+        <v>32.50468473990763</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>38.15071578703105</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>38.02701557629594</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.47216389248049</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.667469851350821</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.92650567904755</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.667469851350821</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.820381227851839</v>
+        <v>1.739656931925348</v>
       </c>
       <c r="C2" t="n">
-        <v>5.463425974133499</v>
+        <v>3.568652904937156</v>
       </c>
       <c r="D2" t="n">
-        <v>25.71000887881547</v>
+        <v>22.58019719767664</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.2514505854742</v>
+        <v>5.718680377237671</v>
       </c>
       <c r="C3" t="n">
-        <v>26.21266370338984</v>
+        <v>12.87562114119692</v>
       </c>
       <c r="D3" t="n">
-        <v>60.41675371934871</v>
+        <v>71.57922511663494</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.64329109265569</v>
+        <v>18.08477445993049</v>
       </c>
       <c r="C4" t="n">
-        <v>55.91347699996859</v>
+        <v>59.0786315984603</v>
       </c>
       <c r="D4" t="n">
-        <v>84.08080038251383</v>
+        <v>109.1084946068778</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.5096755938869</v>
+        <v>21.20575041173111</v>
       </c>
       <c r="C5" t="n">
-        <v>108.9249077861836</v>
+        <v>108.9985388640021</v>
       </c>
       <c r="D5" t="n">
-        <v>74.07286428542186</v>
+        <v>73.48381566287377</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.03531152628644</v>
+        <v>15.41638419978766</v>
       </c>
       <c r="C6" t="n">
-        <v>153.0367956334013</v>
+        <v>89.39892769641881</v>
       </c>
       <c r="D6" t="n">
-        <v>54.6214970211798</v>
+        <v>40.13090090649688</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.23706852727577</v>
+        <v>9.102764713776425</v>
       </c>
       <c r="C7" t="n">
-        <v>177.6236851385584</v>
+        <v>51.86180422454201</v>
       </c>
       <c r="D7" t="n">
-        <v>42.99858595060179</v>
+        <v>32.5184292077671</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.10971906316416</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>145.2004854581033</v>
+        <v>34.54770171244525</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.651561680450389</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>88.08436752043229</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>47.68839473378882</v>
+        <v>35.58835427894688</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>38.57777603837842</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>38.91549724863931</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>38.83695743229957</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.27040689149115</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.845309818955996</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.989027646428</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.825973546325494</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.162430339557228</v>
+        <v>0.8943721585688442</v>
       </c>
       <c r="C2" t="n">
-        <v>6.915430828714532</v>
+        <v>1.432369900496096</v>
       </c>
       <c r="D2" t="n">
-        <v>35.09158994059799</v>
+        <v>15.19549096633213</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.37907778702628</v>
+        <v>6.351907646476864</v>
       </c>
       <c r="C3" t="n">
-        <v>23.6699371493906</v>
+        <v>14.32369900496096</v>
       </c>
       <c r="D3" t="n">
-        <v>64.72171740247097</v>
+        <v>74.9171673110741</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.27768003604838</v>
+        <v>19.38657191576176</v>
       </c>
       <c r="C4" t="n">
-        <v>59.49980136358219</v>
+        <v>52.95252592396021</v>
       </c>
       <c r="D4" t="n">
-        <v>91.22792366943061</v>
+        <v>119.892993138029</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.10501561328796</v>
+        <v>21.27938148954962</v>
       </c>
       <c r="C5" t="n">
-        <v>105.0224606618026</v>
+        <v>123.7983855055228</v>
       </c>
       <c r="D5" t="n">
-        <v>84.4303025652257</v>
+        <v>84.52847733565038</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.3887817575443</v>
+        <v>12.80002656796992</v>
       </c>
       <c r="C6" t="n">
-        <v>162.2141731727005</v>
+        <v>120.1511927842459</v>
       </c>
       <c r="D6" t="n">
-        <v>62.34981494901069</v>
+        <v>40.85543071223103</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.14210104187108</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="C7" t="n">
-        <v>195.8891011760703</v>
+        <v>53.17930964364123</v>
       </c>
       <c r="D7" t="n">
-        <v>47.37030847761284</v>
+        <v>34.07548106670254</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.11939767148639</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>185.1723432365121</v>
+        <v>38.21943812632832</v>
       </c>
       <c r="D8" t="n">
-        <v>40.80634332701867</v>
+        <v>36.71736413883071</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.64531134132641</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>126.2468642799143</v>
+        <v>27.17968519207294</v>
       </c>
       <c r="D9" t="n">
-        <v>36.27655941962388</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>70.89200172366218</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>42.46942393801276</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>31.09685853201771</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.41468274628643</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>18.74450891718435</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.008508305610254</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110.116989202141</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.01063538201282</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.617560363700249</v>
+        <v>0.7706719478337462</v>
       </c>
       <c r="C2" t="n">
-        <v>4.701589755637975</v>
+        <v>7.262969516017903</v>
       </c>
       <c r="D2" t="n">
-        <v>28.69452189972577</v>
+        <v>21.70251475007999</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.28643364992859</v>
+        <v>4.638757902566179</v>
       </c>
       <c r="C3" t="n">
-        <v>36.31484758008951</v>
+        <v>9.154797342101507</v>
       </c>
       <c r="D3" t="n">
-        <v>69.80226177194821</v>
+        <v>70.41094534858125</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.18611545764617</v>
+        <v>16.04273923509713</v>
       </c>
       <c r="C4" t="n">
-        <v>84.97419079337843</v>
+        <v>43.61021477034756</v>
       </c>
       <c r="D4" t="n">
-        <v>89.88783805313372</v>
+        <v>129.8989657397125</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.80800372279091</v>
+        <v>25.52544031041707</v>
       </c>
       <c r="C5" t="n">
-        <v>96.92304210176638</v>
+        <v>111.9928693619549</v>
       </c>
       <c r="D5" t="n">
-        <v>59.93569734426779</v>
+        <v>107.1823056111456</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.51954982419159</v>
+        <v>20.16607959293373</v>
       </c>
       <c r="C6" t="n">
-        <v>129.0065570765522</v>
+        <v>160.6041069377357</v>
       </c>
       <c r="D6" t="n">
-        <v>31.19503330244241</v>
+        <v>56.63407981488576</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.30723027816702</v>
+        <v>8.803331663981149</v>
       </c>
       <c r="C7" t="n">
-        <v>130.1934900509865</v>
+        <v>113.2455794325738</v>
       </c>
       <c r="D7" t="n">
-        <v>28.68568617038755</v>
+        <v>37.60879105428681</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>93.04513866999145</v>
+        <v>54.74225198880214</v>
       </c>
       <c r="D8" t="n">
-        <v>26.70353755551324</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>54.1374954029861</v>
+        <v>36.94218436310322</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>32.59893251951534</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.98534020436108</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>31.02617269731195</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>48.63872651149973</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.461642405174254</v>
+        <v>0.414297531192154</v>
       </c>
       <c r="C2" t="n">
-        <v>2.187333885061894</v>
+        <v>3.198534020436108</v>
       </c>
       <c r="D2" t="n">
-        <v>19.94322286406971</v>
+        <v>15.91020329502381</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.83130362578557</v>
+        <v>3.774819922828986</v>
       </c>
       <c r="C3" t="n">
-        <v>27.71473769088746</v>
+        <v>19.99329199698629</v>
       </c>
       <c r="D3" t="n">
-        <v>75.80074024489623</v>
+        <v>71.72648727227197</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.05245890114836</v>
+        <v>13.464669763745</v>
       </c>
       <c r="C4" t="n">
-        <v>90.0027025345306</v>
+        <v>34.2551408965797</v>
       </c>
       <c r="D4" t="n">
-        <v>102.944100771912</v>
+        <v>137.1099026274053</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.02322745419922</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="C5" t="n">
-        <v>126.9890655443249</v>
+        <v>101.5372563117264</v>
       </c>
       <c r="D5" t="n">
-        <v>73.33655350723674</v>
+        <v>124.117453509403</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.22899356146354</v>
+        <v>25.15728492132452</v>
       </c>
       <c r="C6" t="n">
-        <v>147.200305531654</v>
+        <v>175.9802394816493</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>71.28568255306517</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.34904451882213</v>
+        <v>10.54004335279375</v>
       </c>
       <c r="C7" t="n">
-        <v>156.663371652889</v>
+        <v>162.7119192587536</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>41.98051358129786</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>121.8348900970292</v>
+        <v>82.69751786723006</v>
       </c>
       <c r="D8" t="n">
-        <v>27.87181732356695</v>
+        <v>41.55738032076748</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>59.46249495082079</v>
+        <v>48.47968338341173</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>34.87658719336794</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.413536767666159</v>
+        <v>0.9680032363873551</v>
       </c>
       <c r="C2" t="n">
-        <v>8.591274159863838</v>
+        <v>4.432590884674349</v>
       </c>
       <c r="D2" t="n">
-        <v>20.63830023867645</v>
+        <v>17.07161082914779</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.75214191464007</v>
+        <v>2.542726553999239</v>
       </c>
       <c r="C3" t="n">
-        <v>17.31802950291373</v>
+        <v>15.9288565014045</v>
       </c>
       <c r="D3" t="n">
-        <v>74.75517893987337</v>
+        <v>67.91730617979435</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.02991976167969</v>
+        <v>10.43990508696058</v>
       </c>
       <c r="C4" t="n">
-        <v>80.03501809331273</v>
+        <v>42.55090899746525</v>
       </c>
       <c r="D4" t="n">
-        <v>115.1707866806018</v>
+        <v>141.4619902003314</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.25103397931348</v>
+        <v>24.3473430653209</v>
       </c>
       <c r="C5" t="n">
-        <v>146.0104273141069</v>
+        <v>81.95138961200252</v>
       </c>
       <c r="D5" t="n">
-        <v>89.53539062730911</v>
+        <v>143.1142715865788</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.62271544859552</v>
+        <v>30.51075515258238</v>
       </c>
       <c r="C6" t="n">
-        <v>174.7324381495516</v>
+        <v>171.4318023678738</v>
       </c>
       <c r="D6" t="n">
-        <v>50.59633143376788</v>
+        <v>90.60647737264239</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.43373686329462</v>
+        <v>18.68462230722529</v>
       </c>
       <c r="C7" t="n">
-        <v>183.4326863045868</v>
+        <v>208.8844955371853</v>
       </c>
       <c r="D7" t="n">
-        <v>34.43480072645687</v>
+        <v>50.96350507515617</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.59934912567606</v>
+        <v>7.260024272905162</v>
       </c>
       <c r="C8" t="n">
-        <v>162.6412334240478</v>
+        <v>143.2811686963007</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>43.39324852770901</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.660937189136355</v>
       </c>
       <c r="C9" t="n">
-        <v>99.7328040313207</v>
+        <v>73.99530621678632</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>43.4874963073167</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>49.39663573917827</v>
+        <v>44.12955930589413</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>34.47308888692249</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.93999988351647</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>43.39815726623026</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.02534551386117</v>
+        <v>0.626355035309465</v>
       </c>
       <c r="C2" t="n">
-        <v>3.942698780255191</v>
+        <v>2.198133109808608</v>
       </c>
       <c r="D2" t="n">
-        <v>14.22454248683204</v>
+        <v>12.15403657857551</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.4968875115359</v>
+        <v>3.926990816987242</v>
       </c>
       <c r="C3" t="n">
-        <v>25.57943643415064</v>
+        <v>18.96736564604837</v>
       </c>
       <c r="D3" t="n">
-        <v>76.14435194138262</v>
+        <v>74.14649536324036</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.50137964389641</v>
+        <v>16.7446888436336</v>
       </c>
       <c r="C4" t="n">
-        <v>75.05755723278139</v>
+        <v>58.6064109527176</v>
       </c>
       <c r="D4" t="n">
-        <v>126.3509295365645</v>
+        <v>147.7795366771596</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.01817984695774</v>
+        <v>19.43860454408685</v>
       </c>
       <c r="C5" t="n">
-        <v>169.4741974456057</v>
+        <v>133.5422314701724</v>
       </c>
       <c r="D5" t="n">
-        <v>94.78774084502956</v>
+        <v>132.6095711511379</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.62521872335175</v>
+        <v>11.59247689174634</v>
       </c>
       <c r="C6" t="n">
-        <v>215.1048489912932</v>
+        <v>184.5940938387108</v>
       </c>
       <c r="D6" t="n">
-        <v>49.79129831628549</v>
+        <v>75.23034482872885</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.665486074759095</v>
+        <v>4.790928796724434</v>
       </c>
       <c r="C7" t="n">
-        <v>199.9613906532861</v>
+        <v>100.7292779511312</v>
       </c>
       <c r="D7" t="n">
-        <v>34.43480072645687</v>
+        <v>38.50709020367265</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>2.503456645829366</v>
       </c>
       <c r="C8" t="n">
-        <v>124.5052438525805</v>
+        <v>54.49190632421922</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>37.71874679716245</v>
+        <v>33.61405964570653</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.62008900065227</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>36.55046702910875</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.146100481483527</v>
+        <v>0.3426299487821368</v>
       </c>
       <c r="C2" t="n">
-        <v>5.127668259281091</v>
+        <v>1.606139244147782</v>
       </c>
       <c r="D2" t="n">
-        <v>12.61840324268425</v>
+        <v>9.484664570728436</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.32445976848696</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C3" t="n">
-        <v>20.31726873938774</v>
+        <v>13.16523671394973</v>
       </c>
       <c r="D3" t="n">
-        <v>70.34222300928397</v>
+        <v>66.69012154948584</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.62976760897449</v>
+        <v>11.3588209381356</v>
       </c>
       <c r="C4" t="n">
-        <v>70.10562181256049</v>
+        <v>50.48932093400496</v>
       </c>
       <c r="D4" t="n">
-        <v>134.1872397118625</v>
+        <v>145.2525180864283</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.40583132141499</v>
+        <v>18.03961406553514</v>
       </c>
       <c r="C5" t="n">
-        <v>154.6007197262665</v>
+        <v>109.4403253309132</v>
       </c>
       <c r="D5" t="n">
-        <v>115.5762484824558</v>
+        <v>140.5617275555371</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.11831811279092</v>
+        <v>11.75348351524281</v>
       </c>
       <c r="C6" t="n">
-        <v>244.408054467652</v>
+        <v>166.9236169099725</v>
       </c>
       <c r="D6" t="n">
-        <v>63.31585468998956</v>
+        <v>81.26809320984674</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.88802400845363</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>250.0265965790564</v>
+        <v>129.594623951396</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>38.5669768136317</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>185.506137455956</v>
+        <v>59.58226817073891</v>
       </c>
       <c r="D8" t="n">
-        <v>32.62838495064274</v>
+        <v>27.87181732356695</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>79.76405572694058</v>
+        <v>31.06249736236907</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>21.74374815365835</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>34.16482010778901</v>
+        <v>19.78712497909446</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>20.35653864755762</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>14.21570675749381</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.515818455357075</v>
+        <v>0.5713771638716436</v>
       </c>
       <c r="C2" t="n">
-        <v>3.865140711619692</v>
+        <v>4.042837046088365</v>
       </c>
       <c r="D2" t="n">
-        <v>9.012443924985719</v>
+        <v>14.16171063376024</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.743845964649594</v>
+        <v>1.978221624057323</v>
       </c>
       <c r="C3" t="n">
-        <v>20.54797944988574</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="D3" t="n">
-        <v>65.64456024446297</v>
+        <v>59.18466035051896</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.82647700272235</v>
+        <v>8.461683462903258</v>
       </c>
       <c r="C4" t="n">
-        <v>63.53282093262809</v>
+        <v>40.39400929123502</v>
       </c>
       <c r="D4" t="n">
-        <v>137.9394794374938</v>
+        <v>144.8441110414616</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.74377351585415</v>
+        <v>18.06415775814131</v>
       </c>
       <c r="C5" t="n">
-        <v>148.612058730361</v>
+        <v>100.2855279888117</v>
       </c>
       <c r="D5" t="n">
-        <v>130.6706194352505</v>
+        <v>162.9210315197582</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.2026095466359</v>
+        <v>18.43525839034661</v>
       </c>
       <c r="C6" t="n">
-        <v>257.5300942826149</v>
+        <v>173.3638818498316</v>
       </c>
       <c r="D6" t="n">
-        <v>74.66682164649117</v>
+        <v>107.351166216276</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.86995163914969</v>
+        <v>9.042878103817369</v>
       </c>
       <c r="C7" t="n">
-        <v>296.019513027611</v>
+        <v>192.4755644084042</v>
       </c>
       <c r="D7" t="n">
-        <v>43.89688509998763</v>
+        <v>53.05953642372311</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>2.837250865273282</v>
       </c>
       <c r="C8" t="n">
-        <v>231.2359455197725</v>
+        <v>119.4148820060608</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>31.62700229231099</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>94.96249193638545</v>
+        <v>53.47187045950676</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>23.74062298409636</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>34.59188035913637</v>
+        <v>28.75539025738908</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>18.30272245027328</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>13.88583952886689</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.695879195861741</v>
+        <v>0.8354672963140357</v>
       </c>
       <c r="C2" t="n">
-        <v>6.645450210046659</v>
+        <v>5.418265579738146</v>
       </c>
       <c r="D2" t="n">
-        <v>10.41339789894592</v>
+        <v>21.082050200996</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.530004891573036</v>
+        <v>1.963495408493621</v>
       </c>
       <c r="C3" t="n">
-        <v>17.96107424919539</v>
+        <v>12.79217258633594</v>
       </c>
       <c r="D3" t="n">
-        <v>58.96867585558466</v>
+        <v>56.78428721363552</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.74691438094935</v>
+        <v>6.024003913258428</v>
       </c>
       <c r="C4" t="n">
-        <v>57.84064774340508</v>
+        <v>30.19659588722339</v>
       </c>
       <c r="D4" t="n">
-        <v>138.4499882437022</v>
+        <v>142.0873634879366</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.22206457427158</v>
+        <v>15.73250696055514</v>
       </c>
       <c r="C5" t="n">
-        <v>134.5976102522377</v>
+        <v>86.46742905153783</v>
       </c>
       <c r="D5" t="n">
-        <v>143.5315143608837</v>
+        <v>176.3709750679395</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.25294072145974</v>
+        <v>21.81639748377262</v>
       </c>
       <c r="C6" t="n">
-        <v>249.8420280106581</v>
+        <v>167.0443718775948</v>
       </c>
       <c r="D6" t="n">
-        <v>92.45805354285189</v>
+        <v>133.4744908785794</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.86534600026472</v>
+        <v>15.4507453694363</v>
       </c>
       <c r="C7" t="n">
-        <v>329.1966949449277</v>
+        <v>224.4550141265397</v>
       </c>
       <c r="D7" t="n">
-        <v>51.98157744446011</v>
+        <v>70.24699348197203</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>299.0796206217483</v>
+        <v>189.3447709795611</v>
       </c>
       <c r="D8" t="n">
-        <v>37.30150402285756</v>
+        <v>37.55184968744049</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>166.6281108509941</v>
+        <v>100.8421789371196</v>
       </c>
       <c r="D9" t="n">
-        <v>33.61405964570653</v>
+        <v>26.29218526743382</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>61.35432277690443</v>
+        <v>45.83780031128358</v>
       </c>
       <c r="D10" t="n">
-        <v>26.76244241776806</v>
+        <v>22.34948648717864</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>25.41057582902019</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>9.316785713302231</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.337361357362409</v>
+        <v>3.073852061996763</v>
       </c>
       <c r="C2" t="n">
-        <v>13.06509844811655</v>
+        <v>3.685480881742526</v>
       </c>
       <c r="D2" t="n">
-        <v>10.36823750455056</v>
+        <v>8.114144775599888</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.906554041647306</v>
+        <v>0.5969026041820606</v>
       </c>
       <c r="C2" t="n">
-        <v>3.721805546799658</v>
+        <v>17.15898637482575</v>
       </c>
       <c r="D2" t="n">
-        <v>7.663522579350602</v>
+        <v>24.7145167067092</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.70595871481147</v>
+        <v>2.390555659840983</v>
       </c>
       <c r="C3" t="n">
-        <v>23.14470212761856</v>
+        <v>17.16094987023424</v>
       </c>
       <c r="D3" t="n">
-        <v>63.51907646476863</v>
+        <v>60.42166245786995</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.05919226635785</v>
+        <v>4.888121819444868</v>
       </c>
       <c r="C4" t="n">
-        <v>81.73245987395545</v>
+        <v>31.08998629808799</v>
       </c>
       <c r="D4" t="n">
-        <v>140.7983287522605</v>
+        <v>137.3013434297334</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.73499453977815</v>
+        <v>12.76272015520854</v>
       </c>
       <c r="C5" t="n">
-        <v>207.0996782108647</v>
+        <v>71.02944640225674</v>
       </c>
       <c r="D5" t="n">
-        <v>132.3395905324701</v>
+        <v>186.8020444255619</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.91198686398306</v>
+        <v>22.01765576314322</v>
       </c>
       <c r="C6" t="n">
-        <v>268.2370347451306</v>
+        <v>153.7210737832613</v>
       </c>
       <c r="D6" t="n">
-        <v>75.06933820523237</v>
+        <v>154.284596965499</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.569454726192155</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="C7" t="n">
-        <v>210.3217741762027</v>
+        <v>232.9589127407256</v>
       </c>
       <c r="D7" t="n">
-        <v>32.81786225756237</v>
+        <v>89.65025510870598</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>11.01520924164921</v>
       </c>
       <c r="C8" t="n">
-        <v>122.7528242004999</v>
+        <v>243.6697801940583</v>
       </c>
       <c r="D8" t="n">
-        <v>24.70077223884975</v>
+        <v>45.98015372839936</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>3.660937189136355</v>
       </c>
       <c r="C9" t="n">
-        <v>46.81562102471339</v>
+        <v>164.2984235488164</v>
       </c>
       <c r="D9" t="n">
-        <v>20.41249826669968</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>22.776546738526</v>
+        <v>79.29085333349366</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.17036643664921</v>
+        <v>37.13853390395258</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.90198946049134</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>16.05550195525234</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>10.40652566501619</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.609305471438775</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.7166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.985715752792803</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C2" t="n">
-        <v>6.635632733004192</v>
+        <v>7.063674732055801</v>
       </c>
       <c r="D2" t="n">
-        <v>14.08906130364598</v>
+        <v>28.82607609209484</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.21861094287755</v>
+        <v>5.085453107998478</v>
       </c>
       <c r="C3" t="n">
-        <v>32.92290926191679</v>
+        <v>7.274750488468865</v>
       </c>
       <c r="D3" t="n">
-        <v>11.84478605173777</v>
+        <v>8.580474935117122</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.46881773874025</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.44074796594459</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39723522623283</v>
+        <v>11.6789730139434</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13846677263071</v>
+        <v>59.95206147157613</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576145320733274</v>
+        <v>0.7785982009295601</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.255876297909923</v>
+        <v>2.273727683035613</v>
       </c>
       <c r="C2" t="n">
-        <v>6.764241682260523</v>
+        <v>3.706097583531709</v>
       </c>
       <c r="D2" t="n">
-        <v>24.6241959179185</v>
+        <v>21.28821721888783</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.05648370295658</v>
+        <v>11.54535300194249</v>
       </c>
       <c r="C3" t="n">
-        <v>28.51486206984861</v>
+        <v>20.80814259151115</v>
       </c>
       <c r="D3" t="n">
-        <v>20.81305133003238</v>
+        <v>31.78899066351172</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.84831213192725</v>
+        <v>6.457936398535519</v>
       </c>
       <c r="C4" t="n">
-        <v>50.70628717664351</v>
+        <v>12.4053639908627</v>
       </c>
       <c r="D4" t="n">
-        <v>21.27545449873262</v>
+        <v>18.69738502738051</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>21.07812321017901</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43803786579395</v>
+        <v>13.63080706030517</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12800072495571</v>
+        <v>73.76672056165152</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250113234903989</v>
+        <v>1.603624360035903</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.4172838320339</v>
+        <v>3.034582153826891</v>
       </c>
       <c r="C2" t="n">
-        <v>7.563384313517426</v>
+        <v>2.928553401768235</v>
       </c>
       <c r="D2" t="n">
-        <v>19.75669080026281</v>
+        <v>26.25095186385546</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.45270886484479</v>
+        <v>9.44932165337555</v>
       </c>
       <c r="C3" t="n">
-        <v>27.18950266911541</v>
+        <v>16.72898088036565</v>
       </c>
       <c r="D3" t="n">
-        <v>35.68162031085032</v>
+        <v>41.98934931063608</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.96464138711389</v>
+        <v>15.9916883544763</v>
       </c>
       <c r="C4" t="n">
-        <v>62.2054980364864</v>
+        <v>37.35648189429538</v>
       </c>
       <c r="D4" t="n">
-        <v>26.92933952749001</v>
+        <v>30.83473189498382</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.891108120286615</v>
+        <v>6.528622233241291</v>
       </c>
       <c r="C5" t="n">
-        <v>55.73872590861267</v>
+        <v>15.95340019401067</v>
       </c>
       <c r="D5" t="n">
-        <v>30.31146036862028</v>
+        <v>26.8262560185441</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.45733986592554</v>
+        <v>24.03318379996192</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.29531043699581</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72590788485543</v>
+        <v>14.84502001789287</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0280380976181</v>
+        <v>87.42067343870248</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181476971213858</v>
+        <v>2.474170002982146</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.785038310498954</v>
+        <v>2.607521902479529</v>
       </c>
       <c r="C2" t="n">
-        <v>5.911102927270045</v>
+        <v>5.256277208537423</v>
       </c>
       <c r="D2" t="n">
-        <v>18.7454906648886</v>
+        <v>22.03238197870692</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.07259257685203</v>
+        <v>10.09236639965721</v>
       </c>
       <c r="C3" t="n">
-        <v>28.38232612977529</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="D3" t="n">
-        <v>42.76002125846983</v>
+        <v>53.24508673982577</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.03594911662541</v>
+        <v>17.54874021341173</v>
       </c>
       <c r="C4" t="n">
-        <v>64.78356750783853</v>
+        <v>40.11322944782042</v>
       </c>
       <c r="D4" t="n">
-        <v>38.10948238345269</v>
+        <v>44.63123238276425</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.40209995258047</v>
+        <v>15.75705065316131</v>
       </c>
       <c r="C5" t="n">
-        <v>87.69461368184635</v>
+        <v>46.73119072214818</v>
       </c>
       <c r="D5" t="n">
-        <v>32.79037332184348</v>
+        <v>32.22586839190156</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.579894098040377</v>
+        <v>6.883033154474389</v>
       </c>
       <c r="C6" t="n">
-        <v>51.64287448649497</v>
+        <v>18.75727163733956</v>
       </c>
       <c r="D6" t="n">
-        <v>38.27932473628739</v>
+        <v>33.85164259013428</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>28.06718511671205</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04309204609487</v>
+        <v>16.09425981417728</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7096957292856</v>
+        <v>101.6479567211197</v>
       </c>
       <c r="D21" t="n">
-        <v>6.014364015364956</v>
+        <v>3.388265224037323</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.995132319207771</v>
+        <v>2.357176237896592</v>
       </c>
       <c r="C2" t="n">
-        <v>5.746169312956581</v>
+        <v>6.69159235214626</v>
       </c>
       <c r="D2" t="n">
-        <v>17.15309588860027</v>
+        <v>32.70987001009523</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.78021168743573</v>
+        <v>9.47386534598172</v>
       </c>
       <c r="C3" t="n">
-        <v>23.74847696573034</v>
+        <v>17.61746255270901</v>
       </c>
       <c r="D3" t="n">
-        <v>44.68424675879358</v>
+        <v>59.02758071783948</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.51794618168159</v>
+        <v>18.79948678862217</v>
       </c>
       <c r="C4" t="n">
-        <v>56.98554549300611</v>
+        <v>36.41204060280995</v>
       </c>
       <c r="D4" t="n">
-        <v>43.86546917345174</v>
+        <v>59.94649656901449</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.4077694546277</v>
+        <v>21.23029410433728</v>
       </c>
       <c r="C5" t="n">
-        <v>76.96902001294994</v>
+        <v>62.09554229361077</v>
       </c>
       <c r="D5" t="n">
-        <v>31.14594591723007</v>
+        <v>41.01251034491051</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.50568218314512</v>
+        <v>14.36984114706057</v>
       </c>
       <c r="C6" t="n">
-        <v>65.44919245131787</v>
+        <v>48.5434969841878</v>
       </c>
       <c r="D6" t="n">
-        <v>31.11452999069417</v>
+        <v>36.30699359845555</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>7.545712854840985</v>
       </c>
       <c r="C7" t="n">
-        <v>30.30262463928205</v>
+        <v>22.81679839440012</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>37.18958478457343</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.03456645829366</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>38.2734342500619</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.048254877495123</v>
+        <v>17.37457188301847</v>
       </c>
       <c r="C21" t="n">
-        <v>66.07738947651677</v>
+        <v>115.5409030220728</v>
       </c>
       <c r="D21" t="n">
-        <v>4.405159298434452</v>
+        <v>4.343642970754618</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.283766144256333</v>
+        <v>1.663080610994097</v>
       </c>
       <c r="C2" t="n">
-        <v>7.456373813754525</v>
+        <v>4.851797154387737</v>
       </c>
       <c r="D2" t="n">
-        <v>17.26305163147591</v>
+        <v>26.57983734477815</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.42954783057037</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C3" t="n">
-        <v>22.91399141712056</v>
+        <v>22.23167676266902</v>
       </c>
       <c r="D3" t="n">
-        <v>48.29707831042184</v>
+        <v>70.01333752836129</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.99766095615978</v>
+        <v>18.40384246381071</v>
       </c>
       <c r="C4" t="n">
-        <v>58.67022455349363</v>
+        <v>40.16428032844126</v>
       </c>
       <c r="D4" t="n">
-        <v>56.6792402092811</v>
+        <v>73.70470889632929</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.65445017030091</v>
+        <v>24.91184799526282</v>
       </c>
       <c r="C5" t="n">
-        <v>94.46867284114934</v>
+        <v>64.81989217289566</v>
       </c>
       <c r="D5" t="n">
-        <v>40.91433557448583</v>
+        <v>52.59713325502288</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.79752329321368</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="C6" t="n">
-        <v>99.05932510620744</v>
+        <v>74.1032984642535</v>
       </c>
       <c r="D6" t="n">
-        <v>34.49566908412018</v>
+        <v>40.49316580936395</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.282424543653592</v>
+        <v>12.33664165156542</v>
       </c>
       <c r="C7" t="n">
-        <v>67.73175586369169</v>
+        <v>46.53189593818607</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>39.58504918293564</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>31.2097595180061</v>
+        <v>27.87181732356695</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>39.22082078466007</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>39.160934174701</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34243432679967</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.7341359652609</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>45.34594471145593</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>43.1870815098172</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.267728253829283</v>
+        <v>18.67812418825678</v>
       </c>
       <c r="C21" t="n">
-        <v>75.40268063347881</v>
+        <v>128.9680003474873</v>
       </c>
       <c r="D21" t="n">
-        <v>5.450796190371962</v>
+        <v>5.336606910930508</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.230350857599506</v>
+        <v>1.581595551541612</v>
       </c>
       <c r="C2" t="n">
-        <v>3.937790041733956</v>
+        <v>2.910881943091792</v>
       </c>
       <c r="D2" t="n">
-        <v>17.58408313076462</v>
+        <v>20.76003695400305</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.63218876827272</v>
+        <v>12.16385405561798</v>
       </c>
       <c r="C3" t="n">
-        <v>26.53664044579129</v>
+        <v>31.08704105497525</v>
       </c>
       <c r="D3" t="n">
-        <v>50.89870972667589</v>
+        <v>77.34699287908495</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.20110371511713</v>
+        <v>11.9586687854304</v>
       </c>
       <c r="C4" t="n">
-        <v>57.94274950464675</v>
+        <v>58.18524118759571</v>
       </c>
       <c r="D4" t="n">
-        <v>68.17845106912399</v>
+        <v>69.05907875983338</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.55122779263475</v>
+        <v>12.00186568441726</v>
       </c>
       <c r="C5" t="n">
-        <v>101.4636252339079</v>
+        <v>44.27682146153116</v>
       </c>
       <c r="D5" t="n">
-        <v>51.68901662859458</v>
+        <v>39.83441309981433</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.89439752076462</v>
+        <v>7.647814616082655</v>
       </c>
       <c r="C6" t="n">
-        <v>127.3964908415874</v>
+        <v>30.63151012020474</v>
       </c>
       <c r="D6" t="n">
-        <v>39.92964262712628</v>
+        <v>26.04282135055514</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.28915790886308</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>109.0535167354399</v>
+        <v>19.58292145661112</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>27.5478405811655</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>62.4195190360122</v>
+        <v>23.44904391593506</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>32.06093477758807</v>
+        <v>26.5140602485936</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.474467557359437</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.0220684649636</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.540159112689508</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
